--- a/VNM_WB_timeseries.xlsx
+++ b/VNM_WB_timeseries.xlsx
@@ -14,15 +14,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
+  <si>
+    <t>External debt stocks (% of GNI)</t>
+  </si>
+  <si>
+    <t>External debt stocks (current US$)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -383,12 +464,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -399,346 +480,2218 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:31">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="D2">
+        <v>-0.584863126277924</v>
+      </c>
+      <c r="E2">
+        <v>3.54799694298148</v>
+      </c>
+      <c r="F2">
+        <v>35.2590740095008</v>
+      </c>
+      <c r="G2">
+        <v>53.9214970089166</v>
+      </c>
+      <c r="H2">
+        <v>41.792625574896</v>
+      </c>
+      <c r="I2">
+        <v>12841178044.2</v>
+      </c>
+      <c r="J2">
         <v>6.78731640463151</v>
       </c>
-      <c r="D2">
+      <c r="K2">
+        <v>2614.11840366563</v>
+      </c>
+      <c r="L2">
+        <v>404.029784055118</v>
+      </c>
+      <c r="M2">
+        <v>5.58792950410756</v>
+      </c>
+      <c r="O2">
+        <v>-0.394297510385513</v>
+      </c>
+      <c r="P2">
+        <v>6.41826259040046</v>
+      </c>
+      <c r="Q2">
+        <v>57.4955974105958</v>
+      </c>
+      <c r="S2">
+        <v>72.746</v>
+      </c>
+      <c r="U2">
+        <v>0.408773571252823</v>
+      </c>
+      <c r="V2">
+        <v>77154011</v>
+      </c>
+      <c r="X2">
+        <v>-0.641752243041992</v>
+      </c>
+      <c r="Y2">
+        <v>-0.345562547445297</v>
+      </c>
+      <c r="Z2">
+        <v>3416511105.0847</v>
+      </c>
+      <c r="AA2">
+        <v>2.26421457232101</v>
+      </c>
+      <c r="AB2">
+        <v>111.417094419512</v>
+      </c>
+      <c r="AC2">
         <v>2.26</v>
       </c>
+      <c r="AD2">
+        <v>24.374</v>
+      </c>
+      <c r="AE2">
+        <v>-1.23829925060272</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:31">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="E3">
+        <v>2.08657136826562</v>
+      </c>
+      <c r="F3">
+        <v>39.2903936255311</v>
+      </c>
+      <c r="G3">
+        <v>55.0619332820827</v>
+      </c>
+      <c r="H3">
+        <v>39.1741871054437</v>
+      </c>
+      <c r="I3">
+        <v>12632834003.6</v>
+      </c>
+      <c r="J3">
         <v>6.19289331233377</v>
       </c>
-      <c r="D3">
+      <c r="K3">
+        <v>2808.83181908363</v>
+      </c>
+      <c r="L3">
+        <v>419.205677580901</v>
+      </c>
+      <c r="M3">
+        <v>5.08240100546193</v>
+      </c>
+      <c r="P3">
+        <v>6.3293821876396</v>
+      </c>
+      <c r="Q3">
+        <v>56.8940047164421</v>
+      </c>
+      <c r="S3">
+        <v>72.98399999999999</v>
+      </c>
+      <c r="V3">
+        <v>77969361</v>
+      </c>
+      <c r="Z3">
+        <v>3674565622.65934</v>
+      </c>
+      <c r="AA3">
+        <v>2.35511336174289</v>
+      </c>
+      <c r="AB3">
+        <v>111.955937998525</v>
+      </c>
+      <c r="AC3">
         <v>2.76</v>
       </c>
+      <c r="AD3">
+        <v>24.937</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:31">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="D4">
+        <v>-0.560990810394287</v>
+      </c>
+      <c r="E4">
+        <v>-1.72255927072095</v>
+      </c>
+      <c r="F4">
+        <v>43.1307744856858</v>
+      </c>
+      <c r="G4">
+        <v>54.7391336880928</v>
+      </c>
+      <c r="H4">
+        <v>38.6816313185181</v>
+      </c>
+      <c r="I4">
+        <v>13342966639.1</v>
+      </c>
+      <c r="J4">
         <v>6.32082099160833</v>
       </c>
-      <c r="D4">
+      <c r="K4">
+        <v>3001.87038766922</v>
+      </c>
+      <c r="L4">
+        <v>445.132861817313</v>
+      </c>
+      <c r="M4">
+        <v>5.23717692306222</v>
+      </c>
+      <c r="N4">
+        <v>37</v>
+      </c>
+      <c r="O4">
+        <v>-0.437316596508026</v>
+      </c>
+      <c r="P4">
+        <v>6.2322449147196</v>
+      </c>
+      <c r="Q4">
+        <v>61.9577349644058</v>
+      </c>
+      <c r="S4">
+        <v>73.13800000000001</v>
+      </c>
+      <c r="U4">
+        <v>0.353681147098541</v>
+      </c>
+      <c r="V4">
+        <v>78772224</v>
+      </c>
+      <c r="W4">
+        <v>43.3</v>
+      </c>
+      <c r="X4">
+        <v>-0.766993641853333</v>
+      </c>
+      <c r="Y4">
+        <v>-0.67900162935257</v>
+      </c>
+      <c r="Z4">
+        <v>4121051660.52162</v>
+      </c>
+      <c r="AA4">
+        <v>2.21304125688085</v>
+      </c>
+      <c r="AB4">
+        <v>116.696868652499</v>
+      </c>
+      <c r="AC4">
         <v>2.12</v>
       </c>
+      <c r="AD4">
+        <v>25.511</v>
+      </c>
+      <c r="AE4">
+        <v>-1.44881856441498</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:31">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="D5">
+        <v>-0.49087256193161</v>
+      </c>
+      <c r="E5">
+        <v>-4.88211706972335</v>
+      </c>
+      <c r="F5">
+        <v>48.37235081336</v>
+      </c>
+      <c r="G5">
+        <v>56.6732579147533</v>
+      </c>
+      <c r="H5">
+        <v>40.0605772555549</v>
+      </c>
+      <c r="I5">
+        <v>15592997724.7</v>
+      </c>
+      <c r="J5">
         <v>6.89906349055258</v>
       </c>
-      <c r="C5">
+      <c r="K5">
+        <v>3239.77125909915</v>
+      </c>
+      <c r="L5">
+        <v>497.117089249256</v>
+      </c>
+      <c r="M5">
+        <v>5.83556100746738</v>
+      </c>
+      <c r="O5">
+        <v>-0.402854233980179</v>
+      </c>
+      <c r="P5">
+        <v>6.32006559696663</v>
+      </c>
+      <c r="Q5">
+        <v>67.6546965243715</v>
+      </c>
+      <c r="R5">
         <v>3.23464817293926</v>
       </c>
-      <c r="D5">
+      <c r="S5">
+        <v>73.236</v>
+      </c>
+      <c r="T5">
+        <v>2.12864112884164</v>
+      </c>
+      <c r="U5">
+        <v>0.126424372196198</v>
+      </c>
+      <c r="V5">
+        <v>79563777</v>
+      </c>
+      <c r="X5">
+        <v>-0.637721121311188</v>
+      </c>
+      <c r="Y5">
+        <v>-0.636823534965515</v>
+      </c>
+      <c r="Z5">
+        <v>6224181087.75992</v>
+      </c>
+      <c r="AA5">
+        <v>2.69483955307833</v>
+      </c>
+      <c r="AB5">
+        <v>124.327954439125</v>
+      </c>
+      <c r="AC5">
         <v>2.25</v>
       </c>
+      <c r="AD5">
+        <v>26.092</v>
+      </c>
+      <c r="AE5">
+        <v>-1.47438275814056</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:31">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="D6">
+        <v>-0.756660282611847</v>
+      </c>
+      <c r="E6">
+        <v>-2.10663701040253</v>
+      </c>
+      <c r="F6">
+        <v>58.7224307884587</v>
+      </c>
+      <c r="G6">
+        <v>59.7310414143857</v>
+      </c>
+      <c r="H6">
+        <v>39.5525077207593</v>
+      </c>
+      <c r="I6">
+        <v>17631234906.8</v>
+      </c>
+      <c r="J6">
         <v>7.53641060890386</v>
       </c>
-      <c r="C6">
+      <c r="K6">
+        <v>3543.09915520461</v>
+      </c>
+      <c r="L6">
+        <v>565.452284586212</v>
+      </c>
+      <c r="M6">
+        <v>6.49878740751187</v>
+      </c>
+      <c r="N6">
+        <v>36.8</v>
+      </c>
+      <c r="O6">
+        <v>-0.47920498251915</v>
+      </c>
+      <c r="P6">
+        <v>6.39096220224323</v>
+      </c>
+      <c r="Q6">
+        <v>73.28545645436159</v>
+      </c>
+      <c r="R6">
         <v>7.75494748709601</v>
       </c>
-      <c r="D6">
+      <c r="S6">
+        <v>73.062</v>
+      </c>
+      <c r="T6">
+        <v>2.01437983970519</v>
+      </c>
+      <c r="U6">
+        <v>0.150153517723083</v>
+      </c>
+      <c r="V6">
+        <v>80338971</v>
+      </c>
+      <c r="W6">
+        <v>30.9</v>
+      </c>
+      <c r="X6">
+        <v>-0.556896567344666</v>
+      </c>
+      <c r="Y6">
+        <v>-0.604071080684662</v>
+      </c>
+      <c r="Z6">
+        <v>7041460609.52428</v>
+      </c>
+      <c r="AA6">
+        <v>2.44283108743254</v>
+      </c>
+      <c r="AB6">
+        <v>133.016497868747</v>
+      </c>
+      <c r="AC6">
         <v>2.14</v>
       </c>
+      <c r="AD6">
+        <v>26.683</v>
+      </c>
+      <c r="AE6">
+        <v>-1.33793187141418</v>
+      </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:31">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
-      <c r="B7">
+      <c r="D7">
+        <v>-0.7295823097228999</v>
+      </c>
+      <c r="E7">
+        <v>-0.971989162897001</v>
+      </c>
+      <c r="F7">
+        <v>60.4667877825079</v>
+      </c>
+      <c r="G7">
+        <v>63.6994926701393</v>
+      </c>
+      <c r="H7">
+        <v>32.8651603081175</v>
+      </c>
+      <c r="I7">
+        <v>18593542977.2</v>
+      </c>
+      <c r="J7">
         <v>7.54724772895918</v>
       </c>
-      <c r="C7">
+      <c r="K7">
+        <v>3893.66509422594</v>
+      </c>
+      <c r="L7">
+        <v>710.746759994861</v>
+      </c>
+      <c r="M7">
+        <v>6.55339711441117</v>
+      </c>
+      <c r="O7">
+        <v>-0.228448659181595</v>
+      </c>
+      <c r="P7">
+        <v>5.46520189802856</v>
+      </c>
+      <c r="Q7">
+        <v>67.0153533748869</v>
+      </c>
+      <c r="R7">
         <v>8.284572431286771</v>
       </c>
-      <c r="D7">
+      <c r="S7">
+        <v>73.19799999999999</v>
+      </c>
+      <c r="T7">
+        <v>1.78096085234042</v>
+      </c>
+      <c r="U7">
+        <v>0.484037667512894</v>
+      </c>
+      <c r="V7">
+        <v>81088313</v>
+      </c>
+      <c r="X7">
+        <v>-0.601215302944183</v>
+      </c>
+      <c r="Y7">
+        <v>-0.317553699016571</v>
+      </c>
+      <c r="Z7">
+        <v>9050561631.215099</v>
+      </c>
+      <c r="AA7">
+        <v>2.6536574396688</v>
+      </c>
+      <c r="AB7">
+        <v>130.714846045026</v>
+      </c>
+      <c r="AC7">
         <v>2.078</v>
       </c>
+      <c r="AD7">
+        <v>27.281</v>
+      </c>
+      <c r="AE7">
+        <v>-1.40304481983185</v>
+      </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:31">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
-      <c r="B8">
+      <c r="D8">
+        <v>-0.747617363929749</v>
+      </c>
+      <c r="E8">
+        <v>-0.246704373698266</v>
+      </c>
+      <c r="F8">
+        <v>65.3595423737595</v>
+      </c>
+      <c r="G8">
+        <v>67.71681432601871</v>
+      </c>
+      <c r="H8">
+        <v>28.8741151356014</v>
+      </c>
+      <c r="I8">
+        <v>18752446327.7</v>
+      </c>
+      <c r="J8">
         <v>6.97795481056711</v>
       </c>
-      <c r="C8">
+      <c r="K8">
+        <v>4237.40088094732</v>
+      </c>
+      <c r="L8">
+        <v>807.7566451170539</v>
+      </c>
+      <c r="M8">
+        <v>5.57239749946528</v>
+      </c>
+      <c r="N8">
+        <v>35.8</v>
+      </c>
+      <c r="O8">
+        <v>-0.24698968231678</v>
+      </c>
+      <c r="P8">
+        <v>5.53277472411016</v>
+      </c>
+      <c r="Q8">
+        <v>70.5968075435795</v>
+      </c>
+      <c r="R8">
         <v>7.41801715108463</v>
       </c>
-      <c r="D8">
+      <c r="S8">
+        <v>73.29300000000001</v>
+      </c>
+      <c r="T8">
+        <v>1.93836458436365</v>
+      </c>
+      <c r="U8">
+        <v>0.405120253562927</v>
+      </c>
+      <c r="V8">
+        <v>82167897</v>
+      </c>
+      <c r="W8">
+        <v>23.7</v>
+      </c>
+      <c r="X8">
+        <v>-0.625979781150818</v>
+      </c>
+      <c r="Y8">
+        <v>-0.518898844718933</v>
+      </c>
+      <c r="Z8">
+        <v>13384067982.157</v>
+      </c>
+      <c r="AA8">
+        <v>3.22464007846191</v>
+      </c>
+      <c r="AB8">
+        <v>138.313621869598</v>
+      </c>
+      <c r="AC8">
         <v>2.046</v>
       </c>
+      <c r="AD8">
+        <v>27.888</v>
+      </c>
+      <c r="AE8">
+        <v>-1.53845131397247</v>
+      </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:31">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
-      <c r="B9">
+      <c r="D9">
+        <v>-0.630165636539459</v>
+      </c>
+      <c r="E9">
+        <v>-8.98165936412439</v>
+      </c>
+      <c r="F9">
+        <v>85.63968738395</v>
+      </c>
+      <c r="G9">
+        <v>70.517874602272</v>
+      </c>
+      <c r="H9">
+        <v>30.7473585616458</v>
+      </c>
+      <c r="I9">
+        <v>23135389256</v>
+      </c>
+      <c r="J9">
         <v>7.12950448605439</v>
       </c>
-      <c r="C9">
+      <c r="K9">
+        <v>4580.79431138427</v>
+      </c>
+      <c r="L9">
+        <v>925.640338348717</v>
+      </c>
+      <c r="M9">
+        <v>5.25231213341748</v>
+      </c>
+      <c r="O9">
+        <v>-0.225955650210381</v>
+      </c>
+      <c r="P9">
+        <v>5.55411627975992</v>
+      </c>
+      <c r="Q9">
+        <v>84.08750939428231</v>
+      </c>
+      <c r="R9">
         <v>8.344448897738371</v>
       </c>
-      <c r="D9">
+      <c r="S9">
+        <v>73.38500000000001</v>
+      </c>
+      <c r="T9">
+        <v>2.30475733676407</v>
+      </c>
+      <c r="U9">
+        <v>0.251871973276138</v>
+      </c>
+      <c r="V9">
+        <v>83633375</v>
+      </c>
+      <c r="X9">
+        <v>-0.57259863615036</v>
+      </c>
+      <c r="Y9">
+        <v>-0.490206182003021</v>
+      </c>
+      <c r="Z9">
+        <v>23479392779.8197</v>
+      </c>
+      <c r="AA9">
+        <v>4.07509843575345</v>
+      </c>
+      <c r="AB9">
+        <v>154.605383996554</v>
+      </c>
+      <c r="AC9">
         <v>2.026</v>
       </c>
+      <c r="AD9">
+        <v>28.504</v>
+      </c>
+      <c r="AE9">
+        <v>-1.52694940567017</v>
+      </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:31">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
+        <v>8.49660483267178</v>
+      </c>
+      <c r="C10">
+        <v>2.15099820496032</v>
+      </c>
+      <c r="D10">
+        <v>-0.711532890796661</v>
+      </c>
+      <c r="E10">
+        <v>-10.9179529896098</v>
+      </c>
+      <c r="F10">
+        <v>82.8727709652009</v>
+      </c>
+      <c r="G10">
+        <v>70.33669194027151</v>
+      </c>
+      <c r="H10">
+        <v>27.5497882153862</v>
+      </c>
+      <c r="I10">
+        <v>26497616052.6</v>
+      </c>
+      <c r="J10">
         <v>5.66177120891362</v>
       </c>
-      <c r="C10">
+      <c r="K10">
+        <v>4844.06704751546</v>
+      </c>
+      <c r="L10">
+        <v>1163.83195772873</v>
+      </c>
+      <c r="M10">
+        <v>3.74838603993047</v>
+      </c>
+      <c r="N10">
+        <v>35.6</v>
+      </c>
+      <c r="O10">
+        <v>-0.199574172496796</v>
+      </c>
+      <c r="P10">
+        <v>5.62508392392053</v>
+      </c>
+      <c r="Q10">
+        <v>83.9807876874868</v>
+      </c>
+      <c r="R10">
         <v>23.1154483474477</v>
       </c>
-      <c r="D10">
+      <c r="S10">
+        <v>73.455</v>
+      </c>
+      <c r="T10">
+        <v>2.15637292727254</v>
+      </c>
+      <c r="U10">
+        <v>0.165260821580887</v>
+      </c>
+      <c r="V10">
+        <v>85175788</v>
+      </c>
+      <c r="W10">
+        <v>17.6</v>
+      </c>
+      <c r="X10">
+        <v>-0.630675971508026</v>
+      </c>
+      <c r="Y10">
+        <v>-0.464453905820847</v>
+      </c>
+      <c r="Z10">
+        <v>23890250550.2909</v>
+      </c>
+      <c r="AA10">
+        <v>3.214583734425</v>
+      </c>
+      <c r="AB10">
+        <v>154.317479627758</v>
+      </c>
+      <c r="AC10">
         <v>1.889</v>
       </c>
+      <c r="AD10">
+        <v>29.128</v>
+      </c>
+      <c r="AE10">
+        <v>-1.49671363830566</v>
+      </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:31">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
+        <v>7.74991935028793</v>
+      </c>
+      <c r="C11">
+        <v>1.79656609383679</v>
+      </c>
+      <c r="D11">
+        <v>-0.545064032077789</v>
+      </c>
+      <c r="E11">
+        <v>-6.23310024019381</v>
+      </c>
+      <c r="F11">
+        <v>103.322353769645</v>
+      </c>
+      <c r="G11">
+        <v>62.6088840664865</v>
+      </c>
+      <c r="H11">
+        <v>32.3054945885018</v>
+      </c>
+      <c r="I11">
+        <v>32773324076.8</v>
+      </c>
+      <c r="J11">
         <v>5.39789754014181</v>
       </c>
-      <c r="C11">
+      <c r="K11">
+        <v>5060.73212267196</v>
+      </c>
+      <c r="L11">
+        <v>1226.16976051536</v>
+      </c>
+      <c r="M11">
+        <v>3.83237459567542</v>
+      </c>
+      <c r="O11">
+        <v>-0.245095103979111</v>
+      </c>
+      <c r="P11">
+        <v>5.77840741696787</v>
+      </c>
+      <c r="Q11">
+        <v>72.0974336552711</v>
+      </c>
+      <c r="R11">
         <v>6.71698269988629</v>
       </c>
-      <c r="D11">
+      <c r="S11">
+        <v>73.52500000000001</v>
+      </c>
+      <c r="T11">
+        <v>2.26520866993266</v>
+      </c>
+      <c r="U11">
+        <v>0.271775960922241</v>
+      </c>
+      <c r="V11">
+        <v>86460018</v>
+      </c>
+      <c r="X11">
+        <v>-0.633366286754608</v>
+      </c>
+      <c r="Y11">
+        <v>-0.531529664993286</v>
+      </c>
+      <c r="Z11">
+        <v>16447104123.628</v>
+      </c>
+      <c r="AA11">
+        <v>2.57418384374192</v>
+      </c>
+      <c r="AB11">
+        <v>134.706317721758</v>
+      </c>
+      <c r="AC11">
         <v>1.737</v>
       </c>
+      <c r="AD11">
+        <v>29.762</v>
+      </c>
+      <c r="AE11">
+        <v>-1.4826385974884</v>
+      </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:31">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
+        <v>6.69884374235195</v>
+      </c>
+      <c r="C12">
+        <v>2.09259938242001</v>
+      </c>
+      <c r="D12">
+        <v>-0.6225432753562929</v>
+      </c>
+      <c r="E12">
+        <v>-2.90486815229253</v>
+      </c>
+      <c r="F12">
+        <v>90.35317010498819</v>
+      </c>
+      <c r="G12">
+        <v>54.1758459668515</v>
+      </c>
+      <c r="H12">
+        <v>31.5643856988691</v>
+      </c>
+      <c r="I12">
+        <v>45021621601.7</v>
+      </c>
+      <c r="J12">
         <v>6.42324482239482</v>
       </c>
-      <c r="C12">
+      <c r="K12">
+        <v>5389.21956993674</v>
+      </c>
+      <c r="L12">
+        <v>1683.16182443979</v>
+      </c>
+      <c r="M12">
+        <v>5.21227683604808</v>
+      </c>
+      <c r="N12">
+        <v>39.3</v>
+      </c>
+      <c r="O12">
+        <v>-0.242955058813095</v>
+      </c>
+      <c r="P12">
+        <v>10.3833082456979</v>
+      </c>
+      <c r="Q12">
+        <v>59.8018415728627</v>
+      </c>
+      <c r="R12">
         <v>9.207466487784149</v>
       </c>
-      <c r="D12">
+      <c r="S12">
+        <v>73.611</v>
+      </c>
+      <c r="T12">
+        <v>1.81539587772715</v>
+      </c>
+      <c r="U12">
+        <v>0.148407876491547</v>
+      </c>
+      <c r="V12">
+        <v>87455152</v>
+      </c>
+      <c r="W12">
+        <v>5.2</v>
+      </c>
+      <c r="X12">
+        <v>-0.631919384002686</v>
+      </c>
+      <c r="Y12">
+        <v>-0.581304907798767</v>
+      </c>
+      <c r="Z12">
+        <v>12466600610.9074</v>
+      </c>
+      <c r="AA12">
+        <v>1.62054734201626</v>
+      </c>
+      <c r="AB12">
+        <v>113.977687539714</v>
+      </c>
+      <c r="AC12">
         <v>1.114</v>
       </c>
+      <c r="AD12">
+        <v>30.417</v>
+      </c>
+      <c r="AE12">
+        <v>-1.49696779251099</v>
+      </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:31">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
+        <v>7.57910664692136</v>
+      </c>
+      <c r="C13">
+        <v>2.79209384764478</v>
+      </c>
+      <c r="D13">
+        <v>-0.614729940891266</v>
+      </c>
+      <c r="E13">
+        <v>0.136736251193688</v>
+      </c>
+      <c r="F13">
+        <v>79.94308182044669</v>
+      </c>
+      <c r="G13">
+        <v>61.1801557211956</v>
+      </c>
+      <c r="H13">
+        <v>32.3778252566617</v>
+      </c>
+      <c r="I13">
+        <v>54317424684.6</v>
+      </c>
+      <c r="J13">
         <v>6.41316889681683</v>
       </c>
-      <c r="C13">
+      <c r="K13">
+        <v>5786.12348870721</v>
+      </c>
+      <c r="L13">
+        <v>1950.92504174913</v>
+      </c>
+      <c r="M13">
+        <v>5.1944977799937</v>
+      </c>
+      <c r="O13">
+        <v>-0.209270849823952</v>
+      </c>
+      <c r="P13">
+        <v>9.980917276184041</v>
+      </c>
+      <c r="Q13">
+        <v>64.0804222196337</v>
+      </c>
+      <c r="R13">
         <v>18.6777322770707</v>
       </c>
-      <c r="D13">
+      <c r="S13">
+        <v>73.71299999999999</v>
+      </c>
+      <c r="T13">
+        <v>1.55654936250578</v>
+      </c>
+      <c r="U13">
+        <v>0.189088448882103</v>
+      </c>
+      <c r="V13">
+        <v>88468314</v>
+      </c>
+      <c r="X13">
+        <v>-0.609958648681641</v>
+      </c>
+      <c r="Y13">
+        <v>-0.541880786418915</v>
+      </c>
+      <c r="Z13">
+        <v>13539119001.0033</v>
+      </c>
+      <c r="AA13">
+        <v>1.4173501296534</v>
+      </c>
+      <c r="AB13">
+        <v>125.260577940829</v>
+      </c>
+      <c r="AC13">
         <v>0.999</v>
       </c>
+      <c r="AD13">
+        <v>31.08</v>
+      </c>
+      <c r="AE13">
+        <v>-1.45916306972504</v>
+      </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:31">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
+        <v>7.97137046755677</v>
+      </c>
+      <c r="C14">
+        <v>3.43791016533393</v>
+      </c>
+      <c r="D14">
+        <v>-0.5321059823036191</v>
+      </c>
+      <c r="E14">
+        <v>4.82078231422777</v>
+      </c>
+      <c r="F14">
+        <v>75.54939137109049</v>
+      </c>
+      <c r="G14">
+        <v>63.4739249038633</v>
+      </c>
+      <c r="H14">
+        <v>32.8737676831763</v>
+      </c>
+      <c r="I14">
+        <v>62250312592.2</v>
+      </c>
+      <c r="J14">
         <v>5.5045447041189</v>
       </c>
-      <c r="C14">
+      <c r="K14">
+        <v>6376.79765706172</v>
+      </c>
+      <c r="L14">
+        <v>2185.11767654291</v>
+      </c>
+      <c r="M14">
+        <v>4.27630507146044</v>
+      </c>
+      <c r="N14">
+        <v>35.6</v>
+      </c>
+      <c r="O14">
+        <v>-0.248135596513748</v>
+      </c>
+      <c r="P14">
+        <v>10.4451862897283</v>
+      </c>
+      <c r="Q14">
+        <v>59.7501918421214</v>
+      </c>
+      <c r="R14">
         <v>9.09470339557193</v>
       </c>
-      <c r="D14">
+      <c r="S14">
+        <v>73.762</v>
+      </c>
+      <c r="T14">
+        <v>1.71831331991755</v>
+      </c>
+      <c r="U14">
+        <v>0.267358660697937</v>
+      </c>
+      <c r="V14">
+        <v>89510356</v>
+      </c>
+      <c r="W14">
+        <v>3.7</v>
+      </c>
+      <c r="X14">
+        <v>-0.676629722118378</v>
+      </c>
+      <c r="Y14">
+        <v>-0.55492377281189</v>
+      </c>
+      <c r="Z14">
+        <v>25573282232.2766</v>
+      </c>
+      <c r="AA14">
+        <v>2.48702822538998</v>
+      </c>
+      <c r="AB14">
+        <v>123.224116745985</v>
+      </c>
+      <c r="AC14">
         <v>1.027</v>
       </c>
+      <c r="AD14">
+        <v>31.752</v>
+      </c>
+      <c r="AE14">
+        <v>-1.42006897926331</v>
+      </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:31">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>7.41635746688502</v>
+      </c>
+      <c r="C15">
+        <v>3.10707263260723</v>
+      </c>
+      <c r="D15">
+        <v>-0.482918798923492</v>
+      </c>
+      <c r="E15">
+        <v>3.62409015316054</v>
+      </c>
+      <c r="F15">
+        <v>77.55811082104751</v>
+      </c>
+      <c r="G15">
+        <v>66.80044599191091</v>
+      </c>
+      <c r="H15">
+        <v>32.1019721650196</v>
+      </c>
+      <c r="I15">
+        <v>66249485456</v>
+      </c>
+      <c r="J15">
         <v>5.55351081026072</v>
       </c>
-      <c r="C15">
+      <c r="K15">
+        <v>6758.40433634749</v>
+      </c>
+      <c r="L15">
+        <v>2359.51736472828</v>
+      </c>
+      <c r="M15">
+        <v>4.31498880369921</v>
+      </c>
+      <c r="O15">
+        <v>-0.245401605963707</v>
+      </c>
+      <c r="P15">
+        <v>10.9161669772076</v>
+      </c>
+      <c r="Q15">
+        <v>64.0459088748316</v>
+      </c>
+      <c r="R15">
         <v>6.59267475899189</v>
       </c>
-      <c r="D15">
+      <c r="S15">
+        <v>73.821</v>
+      </c>
+      <c r="T15">
+        <v>1.74407703676771</v>
+      </c>
+      <c r="U15">
+        <v>0.25057727098465</v>
+      </c>
+      <c r="V15">
+        <v>90573104</v>
+      </c>
+      <c r="X15">
+        <v>-0.65251749753952</v>
+      </c>
+      <c r="Y15">
+        <v>-0.515209794044495</v>
+      </c>
+      <c r="Z15">
+        <v>25893489673.0736</v>
+      </c>
+      <c r="AA15">
+        <v>2.14652156785821</v>
+      </c>
+      <c r="AB15">
+        <v>130.846354866743</v>
+      </c>
+      <c r="AC15">
         <v>1.316</v>
       </c>
+      <c r="AD15">
+        <v>32.429</v>
+      </c>
+      <c r="AE15">
+        <v>-1.36654543876648</v>
+      </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:31">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>6.86384985813915</v>
+      </c>
+      <c r="C16">
+        <v>3.49733108025613</v>
+      </c>
+      <c r="D16">
+        <v>-0.438487648963928</v>
+      </c>
+      <c r="E16">
+        <v>4.00897026449707</v>
+      </c>
+      <c r="F16">
+        <v>80.0010314902415</v>
+      </c>
+      <c r="G16">
+        <v>69.5985759502054</v>
+      </c>
+      <c r="H16">
+        <v>33.2733273586748</v>
+      </c>
+      <c r="I16">
+        <v>74733824699.10001</v>
+      </c>
+      <c r="J16">
         <v>6.42224312118567</v>
       </c>
-      <c r="C16">
+      <c r="K16">
+        <v>7296.8794808738</v>
+      </c>
+      <c r="L16">
+        <v>2546.38464459903</v>
+      </c>
+      <c r="M16">
+        <v>5.13784099364456</v>
+      </c>
+      <c r="N16">
+        <v>34.8</v>
+      </c>
+      <c r="O16">
+        <v>-0.0470734238624573</v>
+      </c>
+      <c r="P16">
+        <v>10.3174617549851</v>
+      </c>
+      <c r="Q16">
+        <v>65.8119455041556</v>
+      </c>
+      <c r="R16">
         <v>4.08455446637623</v>
       </c>
-      <c r="D16">
+      <c r="S16">
+        <v>73.886</v>
+      </c>
+      <c r="T16">
+        <v>1.82295771785959</v>
+      </c>
+      <c r="U16">
+        <v>-0.0223473571240902</v>
+      </c>
+      <c r="V16">
+        <v>91679578</v>
+      </c>
+      <c r="W16">
+        <v>3.4</v>
+      </c>
+      <c r="X16">
+        <v>-0.602058231830597</v>
+      </c>
+      <c r="Y16">
+        <v>-0.360228449106216</v>
+      </c>
+      <c r="Z16">
+        <v>34189368832.6688</v>
+      </c>
+      <c r="AA16">
+        <v>2.53633468509765</v>
+      </c>
+      <c r="AB16">
+        <v>135.410521454361</v>
+      </c>
+      <c r="AC16">
         <v>1.256</v>
       </c>
+      <c r="AD16">
+        <v>33.115</v>
+      </c>
+      <c r="AE16">
+        <v>-1.37489593029022</v>
+      </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:31">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>6.33740826221559</v>
+      </c>
+      <c r="C17">
+        <v>2.75511790461507</v>
+      </c>
+      <c r="D17">
+        <v>-0.457950294017792</v>
+      </c>
+      <c r="E17">
+        <v>-0.853052854546214</v>
+      </c>
+      <c r="F17">
+        <v>90.399227327709</v>
+      </c>
+      <c r="G17">
+        <v>72.9228518369495</v>
+      </c>
+      <c r="H17">
+        <v>36.0278872208547</v>
+      </c>
+      <c r="I17">
+        <v>81825409829.39999</v>
+      </c>
+      <c r="J17">
         <v>6.98715430598611</v>
       </c>
-      <c r="C17">
+      <c r="K17">
+        <v>7671.5819778084</v>
+      </c>
+      <c r="L17">
+        <v>2577.56885340113</v>
+      </c>
+      <c r="M17">
+        <v>5.66896478541561</v>
+      </c>
+      <c r="O17">
+        <v>0.0631621554493904</v>
+      </c>
+      <c r="P17">
+        <v>10.6549127142472</v>
+      </c>
+      <c r="Q17">
+        <v>71.9913763582877</v>
+      </c>
+      <c r="R17">
         <v>0.63120090517572</v>
       </c>
-      <c r="D17">
+      <c r="S17">
+        <v>73.955</v>
+      </c>
+      <c r="T17">
+        <v>1.90702805588388</v>
+      </c>
+      <c r="U17">
+        <v>0.06380822509527211</v>
+      </c>
+      <c r="V17">
+        <v>92823254</v>
+      </c>
+      <c r="X17">
+        <v>-0.505210995674133</v>
+      </c>
+      <c r="Y17">
+        <v>-0.355004519224167</v>
+      </c>
+      <c r="Z17">
+        <v>28250254960.181</v>
+      </c>
+      <c r="AA17">
+        <v>1.8503725793752</v>
+      </c>
+      <c r="AB17">
+        <v>144.914228195237</v>
+      </c>
+      <c r="AC17">
         <v>1.848</v>
       </c>
+      <c r="AD17">
+        <v>33.809</v>
+      </c>
+      <c r="AE17">
+        <v>-1.35883224010468</v>
+      </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:31">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>5.61605826300673</v>
+      </c>
+      <c r="C18">
+        <v>2.63885944068427</v>
+      </c>
+      <c r="D18">
+        <v>-0.490106016397476</v>
+      </c>
+      <c r="E18">
+        <v>0.243099852637275</v>
+      </c>
+      <c r="F18">
+        <v>98.8589607655139</v>
+      </c>
+      <c r="G18">
+        <v>74.10728625561831</v>
+      </c>
+      <c r="H18">
+        <v>37.2437579283185</v>
+      </c>
+      <c r="I18">
+        <v>90484868503.39999</v>
+      </c>
+      <c r="J18">
         <v>6.69000892660424</v>
       </c>
-      <c r="C18">
+      <c r="K18">
+        <v>8374.506845161181</v>
+      </c>
+      <c r="L18">
+        <v>2735.0604380416</v>
+      </c>
+      <c r="M18">
+        <v>5.35427097241221</v>
+      </c>
+      <c r="N18">
+        <v>35.3</v>
+      </c>
+      <c r="O18">
+        <v>-0.0174771249294281</v>
+      </c>
+      <c r="P18">
+        <v>10.3983766667541</v>
+      </c>
+      <c r="Q18">
+        <v>71.3022217174998</v>
+      </c>
+      <c r="R18">
         <v>2.66824816969081</v>
       </c>
-      <c r="D18">
+      <c r="S18">
+        <v>73.98399999999999</v>
+      </c>
+      <c r="T18">
+        <v>1.95056176952778</v>
+      </c>
+      <c r="U18">
+        <v>0.226832523941994</v>
+      </c>
+      <c r="V18">
+        <v>94000117</v>
+      </c>
+      <c r="W18">
+        <v>2.5</v>
+      </c>
+      <c r="X18">
+        <v>-0.502611756324768</v>
+      </c>
+      <c r="Y18">
+        <v>0.0653154402971268</v>
+      </c>
+      <c r="Z18">
+        <v>36527291044.3307</v>
+      </c>
+      <c r="AA18">
+        <v>2.22398532927413</v>
+      </c>
+      <c r="AB18">
+        <v>145.409507973118</v>
+      </c>
+      <c r="AC18">
         <v>1.848</v>
       </c>
+      <c r="AD18">
+        <v>34.51</v>
+      </c>
+      <c r="AE18">
+        <v>-1.37323105335236</v>
+      </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:31">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>5.19387817397176</v>
+      </c>
+      <c r="C19">
+        <v>2.11141959192174</v>
+      </c>
+      <c r="D19">
+        <v>-0.628588140010834</v>
+      </c>
+      <c r="E19">
+        <v>-0.586095207209378</v>
+      </c>
+      <c r="F19">
+        <v>103.972032257471</v>
+      </c>
+      <c r="G19">
+        <v>81.76252183556549</v>
+      </c>
+      <c r="H19">
+        <v>41.5700407851023</v>
+      </c>
+      <c r="I19">
+        <v>109892941227.6</v>
+      </c>
+      <c r="J19">
         <v>6.94019037359206</v>
       </c>
-      <c r="C19">
+      <c r="K19">
+        <v>9169.731920528549</v>
+      </c>
+      <c r="L19">
+        <v>2956.10992127753</v>
+      </c>
+      <c r="M19">
+        <v>5.61787865063133</v>
+      </c>
+      <c r="O19">
+        <v>-0.0333407856523991</v>
+      </c>
+      <c r="P19">
+        <v>10.1349272840895</v>
+      </c>
+      <c r="Q19">
+        <v>79.2175618233041</v>
+      </c>
+      <c r="R19">
         <v>3.52025688811621</v>
       </c>
-      <c r="D19">
+      <c r="S19">
+        <v>74.026</v>
+      </c>
+      <c r="T19">
+        <v>1.80387228671057</v>
+      </c>
+      <c r="U19">
+        <v>0.211102172732353</v>
+      </c>
+      <c r="V19">
+        <v>95176977</v>
+      </c>
+      <c r="X19">
+        <v>-0.433779716491699</v>
+      </c>
+      <c r="Y19">
+        <v>0.0403859280049801</v>
+      </c>
+      <c r="Z19">
+        <v>49075567812.4586</v>
+      </c>
+      <c r="AA19">
+        <v>2.46290138784708</v>
+      </c>
+      <c r="AB19">
+        <v>160.98008365887</v>
+      </c>
+      <c r="AC19">
         <v>1.874</v>
       </c>
+      <c r="AD19">
+        <v>35.213</v>
+      </c>
+      <c r="AE19">
+        <v>-1.41349077224731</v>
+      </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:31">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>5.72640411911641</v>
+      </c>
+      <c r="C20">
+        <v>2.12656065140467</v>
+      </c>
+      <c r="D20">
+        <v>-0.511843025684357</v>
+      </c>
+      <c r="E20">
+        <v>1.90236367538642</v>
+      </c>
+      <c r="F20">
+        <v>105.275984683547</v>
+      </c>
+      <c r="G20">
+        <v>84.4234560833365</v>
+      </c>
+      <c r="H20">
+        <v>38.2696126460405</v>
+      </c>
+      <c r="I20">
+        <v>112622128419.5</v>
+      </c>
+      <c r="J20">
         <v>7.46500685572751</v>
       </c>
-      <c r="C20">
+      <c r="K20">
+        <v>10009.9714756006</v>
+      </c>
+      <c r="L20">
+        <v>3222.31003125366</v>
+      </c>
+      <c r="M20">
+        <v>6.28095828201967</v>
+      </c>
+      <c r="N20">
+        <v>35.7</v>
+      </c>
+      <c r="O20">
+        <v>-0.0117206163704395</v>
+      </c>
+      <c r="P20">
+        <v>9.74588913320742</v>
+      </c>
+      <c r="Q20">
+        <v>80.2404806925565</v>
+      </c>
+      <c r="R20">
         <v>3.53962805942638</v>
       </c>
-      <c r="D20">
+      <c r="S20">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="T20">
+        <v>1.80650138874311</v>
+      </c>
+      <c r="U20">
+        <v>0.0330829620361328</v>
+      </c>
+      <c r="V20">
+        <v>96237319</v>
+      </c>
+      <c r="W20">
+        <v>2.2</v>
+      </c>
+      <c r="X20">
+        <v>-0.372491270303726</v>
+      </c>
+      <c r="Y20">
+        <v>-0.0354671441018581</v>
+      </c>
+      <c r="Z20">
+        <v>55452622582.5609</v>
+      </c>
+      <c r="AA20">
+        <v>2.52957991101101</v>
+      </c>
+      <c r="AB20">
+        <v>164.663936775893</v>
+      </c>
+      <c r="AC20">
         <v>1.161</v>
       </c>
+      <c r="AD20">
+        <v>35.919</v>
+      </c>
+      <c r="AE20">
+        <v>-1.47091710567474</v>
+      </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:31">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>5.76740721151145</v>
+      </c>
+      <c r="C21">
+        <v>1.77330386734804</v>
+      </c>
+      <c r="D21">
+        <v>-0.546221077442169</v>
+      </c>
+      <c r="E21">
+        <v>3.91824395534243</v>
+      </c>
+      <c r="F21">
+        <v>108.031900933361</v>
+      </c>
+      <c r="G21">
+        <v>85.1575874073411</v>
+      </c>
+      <c r="H21">
+        <v>38.5733543617856</v>
+      </c>
+      <c r="I21">
+        <v>122496401626</v>
+      </c>
+      <c r="J21">
         <v>7.35926270105006</v>
       </c>
-      <c r="C21">
+      <c r="K21">
+        <v>11029.2732083963</v>
+      </c>
+      <c r="L21">
+        <v>3440.90025375434</v>
+      </c>
+      <c r="M21">
+        <v>6.32464886581907</v>
+      </c>
+      <c r="O21">
+        <v>0.0278810821473598</v>
+      </c>
+      <c r="P21">
+        <v>9.578836368270901</v>
+      </c>
+      <c r="Q21">
+        <v>79.5466276240668</v>
+      </c>
+      <c r="R21">
         <v>2.79582367452249</v>
       </c>
-      <c r="D21">
+      <c r="S21">
+        <v>74.211</v>
+      </c>
+      <c r="U21">
+        <v>0.0399874038994312</v>
+      </c>
+      <c r="V21">
+        <v>97173776</v>
+      </c>
+      <c r="X21">
+        <v>-0.375260800123215</v>
+      </c>
+      <c r="Y21">
+        <v>-0.050392884761095</v>
+      </c>
+      <c r="Z21">
+        <v>78334835182.60899</v>
+      </c>
+      <c r="AA21">
+        <v>3.36679352940087</v>
+      </c>
+      <c r="AB21">
+        <v>164.704215031408</v>
+      </c>
+      <c r="AC21">
         <v>1.681</v>
       </c>
+      <c r="AD21">
+        <v>36.628</v>
+      </c>
+      <c r="AE21">
+        <v>-1.40485322475433</v>
+      </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:31">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>7.18670543745059</v>
+      </c>
+      <c r="C22">
+        <v>1.87185415971075</v>
+      </c>
+      <c r="D22">
+        <v>-0.374517351388931</v>
+      </c>
+      <c r="E22">
+        <v>4.34486906553373</v>
+      </c>
+      <c r="F22">
+        <v>115.525349937741</v>
+      </c>
+      <c r="G22">
+        <v>84.381598008957</v>
+      </c>
+      <c r="H22">
+        <v>39.0234908853694</v>
+      </c>
+      <c r="I22">
+        <v>129479293168.6</v>
+      </c>
+      <c r="J22">
         <v>2.86541320912272</v>
       </c>
-      <c r="C22">
+      <c r="K22">
+        <v>11609.3177276423</v>
+      </c>
+      <c r="L22">
+        <v>3534.03953482647</v>
+      </c>
+      <c r="M22">
+        <v>1.91581434772165</v>
+      </c>
+      <c r="N22">
+        <v>36.8</v>
+      </c>
+      <c r="O22">
+        <v>0.193557769060135</v>
+      </c>
+      <c r="P22">
+        <v>9.478813283446319</v>
+      </c>
+      <c r="Q22">
+        <v>78.8642648059779</v>
+      </c>
+      <c r="R22">
         <v>3.22093436652516</v>
       </c>
-      <c r="D22">
+      <c r="S22">
+        <v>75.383</v>
+      </c>
+      <c r="U22">
+        <v>-0.0389890633523464</v>
+      </c>
+      <c r="V22">
+        <v>98079191</v>
+      </c>
+      <c r="W22">
+        <v>1.3</v>
+      </c>
+      <c r="X22">
+        <v>-0.236916333436966</v>
+      </c>
+      <c r="Y22">
+        <v>-0.189501881599426</v>
+      </c>
+      <c r="Z22">
+        <v>94833616150.45039</v>
+      </c>
+      <c r="AA22">
+        <v>3.9782956088746</v>
+      </c>
+      <c r="AB22">
+        <v>163.245862814935</v>
+      </c>
+      <c r="AC22">
         <v>2.103</v>
       </c>
+      <c r="AD22">
+        <v>37.34</v>
+      </c>
+      <c r="AE22">
+        <v>-1.37661600112915</v>
+      </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:31">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>7.51457650170697</v>
+      </c>
+      <c r="C23">
+        <v>1.59911146644285</v>
+      </c>
+      <c r="D23">
+        <v>-0.308163285255432</v>
+      </c>
+      <c r="E23">
+        <v>-1.26284279203588</v>
+      </c>
+      <c r="F23">
+        <v>124.282898747665</v>
+      </c>
+      <c r="G23">
+        <v>93.8502071275575</v>
+      </c>
+      <c r="H23">
+        <v>40.2192158810709</v>
+      </c>
+      <c r="I23">
+        <v>139852500394.5</v>
+      </c>
+      <c r="J23">
         <v>2.55372852648131</v>
       </c>
-      <c r="C23">
+      <c r="K23">
+        <v>12048.9019935536</v>
+      </c>
+      <c r="L23">
+        <v>3704.1935590038</v>
+      </c>
+      <c r="M23">
+        <v>1.66651604176819</v>
+      </c>
+      <c r="O23">
+        <v>0.243436112999916</v>
+      </c>
+      <c r="P23">
+        <v>9.585085546437391</v>
+      </c>
+      <c r="Q23">
+        <v>92.8256257092568</v>
+      </c>
+      <c r="R23">
         <v>1.83471554810446</v>
       </c>
-      <c r="D23">
+      <c r="S23">
+        <v>74.145</v>
+      </c>
+      <c r="U23">
+        <v>-0.117782436311245</v>
+      </c>
+      <c r="V23">
+        <v>98935098</v>
+      </c>
+      <c r="X23">
+        <v>-0.404661357402802</v>
+      </c>
+      <c r="Y23">
+        <v>-0.172221630811691</v>
+      </c>
+      <c r="Z23">
+        <v>109371353442.833</v>
+      </c>
+      <c r="AA23">
+        <v>3.68607429495755</v>
+      </c>
+      <c r="AB23">
+        <v>186.675832836814</v>
+      </c>
+      <c r="AC23">
         <v>2.385</v>
       </c>
+      <c r="AD23">
+        <v>38.052</v>
+      </c>
+      <c r="AE23">
+        <v>-1.30874562263489</v>
+      </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:31">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>7.86844456743926</v>
+      </c>
+      <c r="C24">
+        <v>2.32004921223853</v>
+      </c>
+      <c r="D24">
+        <v>-0.287254333496094</v>
+      </c>
+      <c r="E24">
+        <v>0.339101746979362</v>
+      </c>
+      <c r="F24">
+        <v>124.961478822546</v>
+      </c>
+      <c r="G24">
+        <v>93.420129043511</v>
+      </c>
+      <c r="H24">
+        <v>37.5572947770856</v>
+      </c>
+      <c r="I24">
+        <v>146627256492.3</v>
+      </c>
+      <c r="J24">
         <v>8.53750046755788</v>
       </c>
-      <c r="C24">
+      <c r="K24">
+        <v>13905.1536875216</v>
+      </c>
+      <c r="L24">
+        <v>4147.69777213621</v>
+      </c>
+      <c r="M24">
+        <v>7.7256990880817</v>
+      </c>
+      <c r="N24">
+        <v>36.1</v>
+      </c>
+      <c r="O24">
+        <v>0.174635261297226</v>
+      </c>
+      <c r="P24">
+        <v>8.81892224803344</v>
+      </c>
+      <c r="Q24">
+        <v>89.7334901043249</v>
+      </c>
+      <c r="R24">
         <v>3.15650749963127</v>
       </c>
-      <c r="D24">
+      <c r="S24">
+        <v>74.502</v>
+      </c>
+      <c r="U24">
+        <v>-0.0461320951581001</v>
+      </c>
+      <c r="V24">
+        <v>99680655</v>
+      </c>
+      <c r="W24">
+        <v>1.6</v>
+      </c>
+      <c r="X24">
+        <v>-0.429956316947937</v>
+      </c>
+      <c r="Y24">
+        <v>-0.158469453454018</v>
+      </c>
+      <c r="Z24">
+        <v>86539530966.6451</v>
+      </c>
+      <c r="AA24">
+        <v>2.65055544761863</v>
+      </c>
+      <c r="AB24">
+        <v>183.153619147836</v>
+      </c>
+      <c r="AC24">
         <v>1.523</v>
       </c>
+      <c r="AD24">
+        <v>38.766</v>
+      </c>
+      <c r="AE24">
+        <v>-1.28640735149384</v>
+      </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:31">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
-      <c r="B25">
+      <c r="D25">
+        <v>-0.415814280509949</v>
+      </c>
+      <c r="E25">
+        <v>5.94503707253957</v>
+      </c>
+      <c r="G25">
+        <v>86.4674192371297</v>
+      </c>
+      <c r="H25">
+        <v>34.8307361261379</v>
+      </c>
+      <c r="I25">
+        <v>141849555320.9</v>
+      </c>
+      <c r="J25">
         <v>5.06502391455075</v>
       </c>
-      <c r="C25">
+      <c r="K25">
+        <v>15033.8768594355</v>
+      </c>
+      <c r="L25">
+        <v>4323.35031982451</v>
+      </c>
+      <c r="M25">
+        <v>4.36194957647844</v>
+      </c>
+      <c r="O25">
+        <v>0.126466900110245</v>
+      </c>
+      <c r="P25">
+        <v>8.84756445434067</v>
+      </c>
+      <c r="Q25">
+        <v>78.3506520327642</v>
+      </c>
+      <c r="R25">
         <v>3.25289282667661</v>
       </c>
-      <c r="D25">
+      <c r="S25">
+        <v>74.58799999999999</v>
+      </c>
+      <c r="U25">
+        <v>-0.0363807342946529</v>
+      </c>
+      <c r="V25">
+        <v>100352192</v>
+      </c>
+      <c r="X25">
+        <v>-0.382607728242874</v>
+      </c>
+      <c r="Y25">
+        <v>-0.0854718759655952</v>
+      </c>
+      <c r="Z25">
+        <v>92237540812.2468</v>
+      </c>
+      <c r="AA25">
+        <v>3.01759407672039</v>
+      </c>
+      <c r="AB25">
+        <v>164.818071269894</v>
+      </c>
+      <c r="AC25">
         <v>1.645</v>
       </c>
+      <c r="AD25">
+        <v>39.48</v>
+      </c>
+      <c r="AE25">
+        <v>-1.24185371398926</v>
+      </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:31">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="E26">
+        <v>5.88742504866573</v>
+      </c>
+      <c r="J26">
         <v>7.09118746633975</v>
       </c>
-      <c r="C26">
+      <c r="K26">
+        <v>16385.5065565458</v>
+      </c>
+      <c r="L26">
+        <v>4717.29028732449</v>
+      </c>
+      <c r="M26">
+        <v>6.4172854315141</v>
+      </c>
+      <c r="R26">
         <v>3.62109273885847</v>
       </c>
-      <c r="D26">
+      <c r="V26">
+        <v>100987686</v>
+      </c>
+      <c r="Z26">
+        <v>83081854928.1161</v>
+      </c>
+      <c r="AA26">
+        <v>2.37429301997203</v>
+      </c>
+      <c r="AC26">
         <v>1.431</v>
+      </c>
+      <c r="AD26">
+        <v>40.195</v>
       </c>
     </row>
   </sheetData>

--- a/VNM_WB_timeseries.xlsx
+++ b/VNM_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Foreign direct investment, net outflows (BoP, current US$)</t>
+  </si>
+  <si>
+    <t>GDP (current US$)</t>
   </si>
   <si>
     <t>GDP growth (annual %)</t>
@@ -428,12 +431,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -489,8 +492,11 @@
       <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -507,19 +513,22 @@
         <v>180000000</v>
       </c>
       <c r="I2">
+        <v>6471740805.56984</v>
+      </c>
+      <c r="J2">
         <v>5.10091813908369</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>98.79833703114009</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>45.2770843017519</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>81.315697940889</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:20">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -536,22 +545,25 @@
         <v>375190280</v>
       </c>
       <c r="I3">
+        <v>9613369520.41885</v>
+      </c>
+      <c r="J3">
         <v>5.96084393218912</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>143.715270231936</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>36.0319130561748</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>66.9469523941752</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>2.142</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:20">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -568,25 +580,28 @@
         <v>473945860</v>
       </c>
       <c r="I4">
+        <v>9866990236.435869</v>
+      </c>
+      <c r="J4">
         <v>8.64604745934572</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>144.549392371677</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>35.7</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>38.8312893080737</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>73.5768851264792</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>2.11</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:20">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -603,22 +618,25 @@
         <v>926303710</v>
       </c>
       <c r="I5">
+        <v>13180953598.1716</v>
+      </c>
+      <c r="J5">
         <v>8.07273065739605</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>189.418573584332</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>37.4894844843075</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>66.2122671512498</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>2.038</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:20">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -635,22 +653,25 @@
         <v>1944515940</v>
       </c>
       <c r="I6">
+        <v>16286433533.3228</v>
+      </c>
+      <c r="J6">
         <v>8.83898095245374</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>229.857787265757</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>43.4600692982849</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>77.4731979426888</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>1.972</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:20">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -667,28 +688,31 @@
         <v>1780400000</v>
       </c>
       <c r="I7">
+        <v>20736164458.9505</v>
+      </c>
+      <c r="J7">
         <v>9.54048017491264</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>287.802661028593</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>8.18770424479667</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>41.9084105866522</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>1323681930.28787</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>74.7212659206088</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>1.955</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:20">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -711,34 +735,37 @@
         <v>2395000000</v>
       </c>
       <c r="I8">
+        <v>24657470574.7501</v>
+      </c>
+      <c r="J8">
         <v>9.34001749939179</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>337.051231790277</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>8.352570983252219</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>51.8372593774353</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.525695502758026</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>1735897756.92245</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>1.62006323557859</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>92.70574680189389</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>1.93</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:20">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -758,34 +785,37 @@
         <v>2220000000</v>
       </c>
       <c r="I9">
+        <v>26843700441.5482</v>
+      </c>
+      <c r="J9">
         <v>8.1520841433542</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>361.643884085566</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>35.4</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>8.13078122459131</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>51.2417773154392</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>1985854205.99896</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>1.67065693157512</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>94.34448406845161</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>2.87</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:20">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -808,34 +838,37 @@
         <v>1671000000</v>
       </c>
       <c r="I10">
+        <v>27209602050.0452</v>
+      </c>
+      <c r="J10">
         <v>5.76445545848843</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>361.350928411167</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>7.62374071027126</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>52.1529451355476</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.319004893302917</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>2002261884.51771</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>1.68021976323165</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>97.0012485118429</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>2.29</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:20">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -855,31 +888,34 @@
         <v>1412000000</v>
       </c>
       <c r="I11">
+        <v>28683659006.7752</v>
+      </c>
+      <c r="J11">
         <v>4.77358688344989</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>375.994455900496</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>6.78523385890954</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>52.8211606307915</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>3326147673.21608</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>2.81499203601051</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>102.787406603958</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>2.33</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:20">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -902,34 +938,37 @@
         <v>1298000000</v>
       </c>
       <c r="I12">
+        <v>31172518403.3162</v>
+      </c>
+      <c r="J12">
         <v>6.78731640463151</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>404.029784055118</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>6.41826259040046</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>57.4955974105958</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.408773571252823</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>3416511105.0847</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>2.26421457232101</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>111.417094419512</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>2.26</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:20">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -949,31 +988,34 @@
         <v>1300000000</v>
       </c>
       <c r="I13">
+        <v>32685198808.5549</v>
+      </c>
+      <c r="J13">
         <v>6.19289331233377</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>419.205677580901</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>6.3293821876396</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>56.8940047164421</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>3674565622.65934</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>2.35511336174289</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>111.955937998525</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>2.76</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:20">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -996,37 +1038,40 @@
         <v>1400000000</v>
       </c>
       <c r="I14">
+        <v>35064105500.8344</v>
+      </c>
+      <c r="J14">
         <v>6.32082099160833</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>445.132861817313</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>37</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>6.2322449147196</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>61.9577349644058</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.353681147098541</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>4121051660.52162</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>2.21304125688085</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>116.696868652499</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>2.12</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:20">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1049,37 +1094,40 @@
         <v>1450000000</v>
       </c>
       <c r="I15">
+        <v>39552513231.9169</v>
+      </c>
+      <c r="J15">
         <v>6.89906349055258</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>497.117089249256</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>6.32006559696663</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>67.6546965243715</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>3.23464817293926</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.126424372196198</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>6224181087.75992</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>2.69483955307833</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>124.327954439125</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>2.25</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:20">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1102,40 +1150,43 @@
         <v>1610000000</v>
       </c>
       <c r="I16">
+        <v>45427854693.2554</v>
+      </c>
+      <c r="J16">
         <v>7.53641060890386</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>565.452284586212</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>36.8</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>6.39096220224323</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>73.28545645436159</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>7.75494748709601</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.150153517723083</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>7041460609.52428</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>2.44283108743254</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>133.016497868747</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>2.14</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:20">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1161,37 +1212,40 @@
         <v>65000000</v>
       </c>
       <c r="I17">
+        <v>57633255738.1992</v>
+      </c>
+      <c r="J17">
         <v>7.54724772895918</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>710.746759994861</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>5.46520189802856</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>67.0153533748869</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>8.284572431286771</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.484037667512894</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>9050561631.215099</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>2.6536574396688</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>130.714846045026</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>2.078</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:20">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1217,40 +1271,43 @@
         <v>85000000</v>
       </c>
       <c r="I18">
+        <v>66371664817.0436</v>
+      </c>
+      <c r="J18">
         <v>6.97795481056711</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>807.7566451170539</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>35.8</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>5.53277472411016</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>70.5968075435795</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>7.41801715108463</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.405120253562927</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>13384067982.157</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>3.22464007846191</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>138.313621869598</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>2.046</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:20">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1276,37 +1333,40 @@
         <v>184000000</v>
       </c>
       <c r="I19">
+        <v>77414425532.24519</v>
+      </c>
+      <c r="J19">
         <v>7.12950448605439</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>925.640338348717</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>5.55411627975992</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>84.08750939428231</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>8.344448897738371</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.251871973276138</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>23479392779.8197</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>4.07509843575345</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>154.605383996554</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>2.026</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:20">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1332,40 +1392,43 @@
         <v>300000000</v>
       </c>
       <c r="I20">
+        <v>99130304099.1274</v>
+      </c>
+      <c r="J20">
         <v>5.66177120891362</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>1163.83195772873</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>35.6</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>5.62508392392053</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>83.9807876874868</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>23.1154483474477</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.165260821580887</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>23890250550.2909</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>3.214583734425</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>154.317479627758</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>1.889</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:20">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1391,37 +1454,40 @@
         <v>700000000</v>
       </c>
       <c r="I21">
+        <v>106014659565.214</v>
+      </c>
+      <c r="J21">
         <v>5.39789754014181</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>1226.16976051536</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>5.77840741696787</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>72.0974336552711</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>6.71698269988629</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.271775960922241</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>16447104123.628</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>2.57418384374192</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>134.706317721758</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>1.737</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:20">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1447,40 +1513,43 @@
         <v>900000000</v>
       </c>
       <c r="I22">
+        <v>147201173196.979</v>
+      </c>
+      <c r="J22">
         <v>6.42324482239482</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>1683.16182443979</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>39.3</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>10.3833082456979</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>59.8018415728627</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>9.207466487784149</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.148407876491547</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>12466600610.9074</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>1.62054734201626</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>113.977687539714</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>1.114</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:20">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1506,37 +1575,40 @@
         <v>950000000</v>
       </c>
       <c r="I23">
+        <v>172595049183.925</v>
+      </c>
+      <c r="J23">
         <v>6.41316889681683</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>1950.92504174913</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>9.980917276184041</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>64.0804222196337</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>18.6777322770707</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.189088448882103</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>13539119001.0033</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>1.4173501296534</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>125.260577940829</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>0.999</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:20">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1562,40 +1634,43 @@
         <v>1200000000</v>
       </c>
       <c r="I24">
+        <v>195590661129.249</v>
+      </c>
+      <c r="J24">
         <v>5.5045447041189</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>2185.11767654291</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>35.6</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>10.4451862897283</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>59.7501918421214</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>9.09470339557193</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>0.267358660697937</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>25573282232.2766</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>2.48702822538998</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>123.224116745985</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>1.027</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:20">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -1621,37 +1696,40 @@
         <v>1956000000</v>
       </c>
       <c r="I25">
+        <v>213708811665.34</v>
+      </c>
+      <c r="J25">
         <v>5.55351081026072</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>2359.51736472828</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>10.9161669772076</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>64.0459088748316</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>6.59267475899189</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>0.25057727098465</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>25893489673.0736</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>2.14652156785821</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>130.846354866743</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>1.316</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:20">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -1677,40 +1755,43 @@
         <v>1150000000</v>
       </c>
       <c r="I26">
+        <v>233451469642.519</v>
+      </c>
+      <c r="J26">
         <v>6.42224312118567</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>2546.38464459903</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>34.8</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>10.3174617549851</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>65.8119455041556</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>4.08455446637623</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>-0.0223473571240902</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>34189368832.6688</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>2.53633468509765</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>135.410521454361</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>1.256</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:20">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -1736,37 +1817,40 @@
         <v>1100000000</v>
       </c>
       <c r="I27">
+        <v>239258328381.741</v>
+      </c>
+      <c r="J27">
         <v>6.98715430598611</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>2577.56885340113</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>10.6549127142472</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>71.9913763582877</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>0.63120090517572</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>0.06380822509527211</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>28250254960.181</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>1.8503725793752</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>144.914228195237</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>1.848</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:20">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -1792,40 +1876,43 @@
         <v>1000000000</v>
       </c>
       <c r="I28">
+        <v>257096001177.982</v>
+      </c>
+      <c r="J28">
         <v>6.69000892660424</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>2735.0604380416</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>35.3</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>10.3983766667541</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>71.3022217174998</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>2.66824816969081</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>0.226832523941994</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>36527291044.3307</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>2.22398532927413</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>145.409507973118</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>1.848</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:20">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -1851,37 +1938,40 @@
         <v>480000000</v>
       </c>
       <c r="I29">
+        <v>281353605986.903</v>
+      </c>
+      <c r="J29">
         <v>6.94019037359206</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>2956.10992127753</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>10.1349272840895</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>79.2175618233041</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>3.52025688811621</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>0.211102172732353</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>49075567812.4586</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>2.46290138784708</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>160.98008365887</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>1.874</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:20">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -1907,40 +1997,43 @@
         <v>598000000</v>
       </c>
       <c r="I30">
+        <v>310106478394.659</v>
+      </c>
+      <c r="J30">
         <v>7.46500685572751</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>3222.31003125366</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>35.7</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>9.74588913320742</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>80.2404806925565</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>3.53962805942638</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>0.0330829620361328</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>55452622582.5609</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>2.52957991101101</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>164.663936775893</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>1.161</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:20">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -1966,37 +2059,40 @@
         <v>485000000</v>
       </c>
       <c r="I31">
+        <v>334365270496.667</v>
+      </c>
+      <c r="J31">
         <v>7.35926270105006</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>3440.90025375434</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>9.578836368270901</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>79.5466276240668</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>2.79582367452249</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>0.0399874038994312</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>78334835182.60899</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>3.36679352940087</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>164.704215031408</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>1.681</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:20">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2022,40 +2118,43 @@
         <v>380000000</v>
       </c>
       <c r="I32">
+        <v>346615738537.796</v>
+      </c>
+      <c r="J32">
         <v>2.86541320912272</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>3534.03953482647</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>36.8</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>9.478813283446319</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>78.8642648059779</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>3.22093436652516</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>-0.0389890633523464</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>94833616150.45039</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>3.9782956088746</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>163.245862814935</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>2.103</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:20">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2081,37 +2180,40 @@
         <v>319000000</v>
       </c>
       <c r="I33">
+        <v>366474752771.009</v>
+      </c>
+      <c r="J33">
         <v>2.55372852648131</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>3704.1935590038</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>9.585085546437391</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>92.8256257092568</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>1.83471554810446</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>-0.117782436311245</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>109371353442.833</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>3.68607429495755</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>186.675832836814</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <v>2.385</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:20">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2137,40 +2239,43 @@
         <v>2674000000</v>
       </c>
       <c r="I34">
+        <v>413445230668.578</v>
+      </c>
+      <c r="J34">
         <v>8.53750046755788</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>4147.69777213621</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>36.1</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>8.81892224803344</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>89.7334901043249</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>3.15650749963127</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>-0.0461320951581001</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>86539530966.6451</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>2.65055544761863</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>183.153619147836</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>1.523</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:20">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2196,37 +2301,40 @@
         <v>-1550000000</v>
       </c>
       <c r="I35">
+        <v>433857681378.291</v>
+      </c>
+      <c r="J35">
         <v>5.06502391455075</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>4323.35031982451</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>8.84756445434067</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>78.3506520327642</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>3.25289282667661</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>-0.0363807342946529</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>92237540812.2468</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>3.01759407672039</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>164.818071269894</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <v>1.645</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:20">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2240,21 +2348,24 @@
         <v>600000000</v>
       </c>
       <c r="I36">
+        <v>476388230307.175</v>
+      </c>
+      <c r="J36">
         <v>7.09118746633975</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>4717.29028732449</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>3.62109273885847</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>83081854928.1161</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>2.37429301997203</v>
       </c>
-      <c r="S36">
+      <c r="T36">
         <v>1.431</v>
       </c>
     </row>

--- a/VNM_WB_timeseries.xlsx
+++ b/VNM_WB_timeseries.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B2D069-DD03-E440-B70E-481FD65C4D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -64,8 +58,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,18 +76,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -123,33 +111,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +166,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,7 +200,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -256,10 +234,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -432,11 +409,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -477,33 +454,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>-0.58486312627792403</v>
+        <v>-0.584863126277924</v>
       </c>
       <c r="C2">
-        <v>3.5479969429814799</v>
+        <v>3.54799694298148</v>
       </c>
       <c r="D2">
-        <v>53.921497008916603</v>
+        <v>53.9214970089166</v>
       </c>
       <c r="E2">
-        <v>6.7873164046315102</v>
+        <v>6.78731640463151</v>
       </c>
       <c r="F2">
         <v>404.029784055118</v>
       </c>
       <c r="G2">
-        <v>57.495597410595799</v>
+        <v>57.4955974105958</v>
       </c>
       <c r="H2">
         <v>-1.8</v>
       </c>
       <c r="I2">
-        <v>0.40877357125282299</v>
+        <v>0.408773571252823</v>
       </c>
       <c r="J2">
         <v>111.417094419512</v>
@@ -515,30 +492,28 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
         <v>2.08657136826562</v>
       </c>
       <c r="D3">
-        <v>55.061933282082698</v>
+        <v>55.0619332820827</v>
       </c>
       <c r="E3">
-        <v>6.1928933123337702</v>
+        <v>6.19289331233377</v>
       </c>
       <c r="F3">
-        <v>419.20567758090101</v>
+        <v>419.205677580901</v>
       </c>
       <c r="G3">
-        <v>56.894004716442097</v>
+        <v>56.8940047164421</v>
       </c>
       <c r="H3">
         <v>-0.4</v>
       </c>
-      <c r="I3" s="2"/>
       <c r="J3">
         <v>111.955937998525</v>
       </c>
@@ -546,10 +521,10 @@
         <v>25.4</v>
       </c>
       <c r="L3">
-        <v>-2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -557,28 +532,28 @@
         <v>-0.560990810394287</v>
       </c>
       <c r="C4">
-        <v>-1.7225592707209501</v>
+        <v>-1.72255927072095</v>
       </c>
       <c r="D4">
-        <v>54.739133688092799</v>
+        <v>54.7391336880928</v>
       </c>
       <c r="E4">
         <v>6.32082099160833</v>
       </c>
       <c r="F4">
-        <v>445.13286181731303</v>
+        <v>445.132861817313</v>
       </c>
       <c r="G4">
-        <v>61.957734964405802</v>
+        <v>61.9577349644058</v>
       </c>
       <c r="H4">
         <v>3.8</v>
       </c>
       <c r="I4">
-        <v>0.35368114709854098</v>
+        <v>0.353681147098541</v>
       </c>
       <c r="J4">
-        <v>116.69686865249901</v>
+        <v>116.696868652499</v>
       </c>
       <c r="K4">
         <v>27.7</v>
@@ -587,7 +562,7 @@
         <v>-1.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
@@ -595,28 +570,28 @@
         <v>-0.49087256193161</v>
       </c>
       <c r="C5">
-        <v>-4.8821170697233498</v>
+        <v>-4.88211706972335</v>
       </c>
       <c r="D5">
         <v>56.6732579147533</v>
       </c>
       <c r="E5">
-        <v>6.8990634905525798</v>
+        <v>6.89906349055258</v>
       </c>
       <c r="F5">
-        <v>497.11708924925603</v>
+        <v>497.117089249256</v>
       </c>
       <c r="G5">
-        <v>67.654696524371502</v>
+        <v>67.6546965243715</v>
       </c>
       <c r="H5">
-        <v>3.2346481729392602</v>
+        <v>3.23464817293926</v>
       </c>
       <c r="I5">
-        <v>0.12642437219619801</v>
+        <v>0.126424372196198</v>
       </c>
       <c r="J5">
-        <v>124.32795443912499</v>
+        <v>124.327954439125</v>
       </c>
       <c r="K5">
         <v>29.8</v>
@@ -625,12 +600,12 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>-0.75666028261184703</v>
+        <v>-0.756660282611847</v>
       </c>
       <c r="C6">
         <v>-2.10663701040253</v>
@@ -639,16 +614,16 @@
         <v>59.7310414143857</v>
       </c>
       <c r="E6">
-        <v>7.5364106089038598</v>
+        <v>7.53641060890386</v>
       </c>
       <c r="F6">
-        <v>565.45228458621204</v>
+        <v>565.452284586212</v>
       </c>
       <c r="G6">
-        <v>73.285456454361594</v>
+        <v>73.28545645436159</v>
       </c>
       <c r="H6">
-        <v>7.7549474870960102</v>
+        <v>7.75494748709601</v>
       </c>
       <c r="I6">
         <v>0.150153517723083</v>
@@ -663,36 +638,36 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>-0.72958230972289995</v>
+        <v>-0.7295823097228999</v>
       </c>
       <c r="C7">
-        <v>-0.97198916289700099</v>
+        <v>-0.971989162897001</v>
       </c>
       <c r="D7">
         <v>63.6994926701393</v>
       </c>
       <c r="E7">
-        <v>7.5472477289591797</v>
+        <v>7.54724772895918</v>
       </c>
       <c r="F7">
-        <v>710.74675999486101</v>
+        <v>710.746759994861</v>
       </c>
       <c r="G7">
-        <v>67.015353374886899</v>
+        <v>67.0153533748869</v>
       </c>
       <c r="H7">
-        <v>8.2845724312867706</v>
+        <v>8.284572431286771</v>
       </c>
       <c r="I7">
-        <v>0.48403766751289401</v>
+        <v>0.484037667512894</v>
       </c>
       <c r="J7">
-        <v>130.71484604502601</v>
+        <v>130.714846045026</v>
       </c>
       <c r="K7">
         <v>28.7</v>
@@ -701,36 +676,36 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>-0.74761736392974898</v>
+        <v>-0.747617363929749</v>
       </c>
       <c r="C8">
-        <v>-0.24670437369826601</v>
+        <v>-0.246704373698266</v>
       </c>
       <c r="D8">
-        <v>67.716814326018707</v>
+        <v>67.71681432601871</v>
       </c>
       <c r="E8">
-        <v>6.9779548105671099</v>
+        <v>6.97795481056711</v>
       </c>
       <c r="F8">
-        <v>807.75664511705395</v>
+        <v>807.7566451170539</v>
       </c>
       <c r="G8">
-        <v>70.596807543579501</v>
+        <v>70.5968075435795</v>
       </c>
       <c r="H8">
         <v>7.41801715108463</v>
       </c>
       <c r="I8">
-        <v>0.40512025356292702</v>
+        <v>0.405120253562927</v>
       </c>
       <c r="J8">
-        <v>138.31362186959799</v>
+        <v>138.313621869598</v>
       </c>
       <c r="K8">
         <v>30.2</v>
@@ -739,74 +714,74 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>-0.63016563653945901</v>
+        <v>-0.630165636539459</v>
       </c>
       <c r="C9">
-        <v>-8.9816593641243898</v>
+        <v>-8.98165936412439</v>
       </c>
       <c r="D9">
-        <v>70.517874602272002</v>
+        <v>70.517874602272</v>
       </c>
       <c r="E9">
-        <v>7.1295044860543904</v>
+        <v>7.12950448605439</v>
       </c>
       <c r="F9">
-        <v>925.64033834871702</v>
+        <v>925.640338348717</v>
       </c>
       <c r="G9">
-        <v>84.087509394282307</v>
+        <v>84.08750939428231</v>
       </c>
       <c r="H9">
-        <v>8.3444488977383706</v>
+        <v>8.344448897738371</v>
       </c>
       <c r="I9">
-        <v>0.25187197327613797</v>
+        <v>0.251871973276138</v>
       </c>
       <c r="J9">
         <v>154.605383996554</v>
       </c>
       <c r="K9">
-        <v>32.200000000000003</v>
+        <v>32.2</v>
       </c>
       <c r="L9">
         <v>-1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>-0.71153289079666104</v>
+        <v>-0.711532890796661</v>
       </c>
       <c r="C10">
         <v>-10.9179529896098</v>
       </c>
       <c r="D10">
-        <v>70.336691940271507</v>
+        <v>70.33669194027151</v>
       </c>
       <c r="E10">
-        <v>5.6617712089136196</v>
+        <v>5.66177120891362</v>
       </c>
       <c r="F10">
         <v>1163.83195772873</v>
       </c>
       <c r="G10">
-        <v>83.980787687486796</v>
+        <v>83.9807876874868</v>
       </c>
       <c r="H10">
         <v>23.1154483474477</v>
       </c>
       <c r="I10">
-        <v>0.16526082158088701</v>
+        <v>0.165260821580887</v>
       </c>
       <c r="J10">
-        <v>154.31747962775799</v>
+        <v>154.317479627758</v>
       </c>
       <c r="K10">
         <v>31</v>
@@ -815,170 +790,170 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>-0.54506403207778897</v>
+        <v>-0.545064032077789</v>
       </c>
       <c r="C11">
         <v>-6.23310024019381</v>
       </c>
       <c r="D11">
-        <v>62.608884066486503</v>
+        <v>62.6088840664865</v>
       </c>
       <c r="E11">
-        <v>5.3978975401418099</v>
+        <v>5.39789754014181</v>
       </c>
       <c r="F11">
-        <v>1226.1697605153599</v>
+        <v>1226.16976051536</v>
       </c>
       <c r="G11">
-        <v>72.097433655271104</v>
+        <v>72.0974336552711</v>
       </c>
       <c r="H11">
         <v>6.71698269988629</v>
       </c>
       <c r="I11">
-        <v>0.27177596092224099</v>
+        <v>0.271775960922241</v>
       </c>
       <c r="J11">
-        <v>134.70631772175801</v>
+        <v>134.706317721758</v>
       </c>
       <c r="K11">
-        <v>36.200000000000003</v>
+        <v>36.2</v>
       </c>
       <c r="L11">
         <v>-4.8</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
-        <v>-0.62254327535629295</v>
+        <v>-0.6225432753562929</v>
       </c>
       <c r="C12">
-        <v>-2.9048681522925301</v>
+        <v>-2.90486815229253</v>
       </c>
       <c r="D12">
-        <v>54.175845966851497</v>
+        <v>54.1758459668515</v>
       </c>
       <c r="E12">
-        <v>6.4232448223948202</v>
+        <v>6.42324482239482</v>
       </c>
       <c r="F12">
-        <v>1683.1618244397901</v>
+        <v>1683.16182443979</v>
       </c>
       <c r="G12">
-        <v>59.801841572862699</v>
+        <v>59.8018415728627</v>
       </c>
       <c r="H12">
-        <v>9.2074664877841492</v>
+        <v>9.207466487784149</v>
       </c>
       <c r="I12">
-        <v>0.14840787649154699</v>
+        <v>0.148407876491547</v>
       </c>
       <c r="J12">
         <v>113.977687539714</v>
       </c>
       <c r="K12">
-        <v>37.299999999999997</v>
+        <v>37.3</v>
       </c>
       <c r="L12">
-        <v>-2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>-0.61472994089126598</v>
+        <v>-0.614729940891266</v>
       </c>
       <c r="C13">
-        <v>0.13673625119368801</v>
+        <v>0.136736251193688</v>
       </c>
       <c r="D13">
-        <v>61.180155721195597</v>
+        <v>61.1801557211956</v>
       </c>
       <c r="E13">
-        <v>6.4131688968168303</v>
+        <v>6.41316889681683</v>
       </c>
       <c r="F13">
-        <v>1950.9250417491301</v>
+        <v>1950.92504174913</v>
       </c>
       <c r="G13">
-        <v>64.080422219633704</v>
+        <v>64.0804222196337</v>
       </c>
       <c r="H13">
-        <v>18.677732277070699</v>
+        <v>18.6777322770707</v>
       </c>
       <c r="I13">
-        <v>0.18908844888210299</v>
+        <v>0.189088448882103</v>
       </c>
       <c r="J13">
-        <v>125.26057794082899</v>
+        <v>125.260577940829</v>
       </c>
       <c r="K13">
-        <v>36.200000000000003</v>
+        <v>36.2</v>
       </c>
       <c r="L13">
         <v>-0.9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>-0.53210598230361905</v>
+        <v>-0.5321059823036191</v>
       </c>
       <c r="C14">
-        <v>4.8207823142277704</v>
+        <v>4.82078231422777</v>
       </c>
       <c r="D14">
-        <v>63.473924903863299</v>
+        <v>63.4739249038633</v>
       </c>
       <c r="E14">
-        <v>5.5045447041189002</v>
+        <v>5.5045447041189</v>
       </c>
       <c r="F14">
         <v>2185.11767654291</v>
       </c>
       <c r="G14">
-        <v>59.750191842121403</v>
+        <v>59.7501918421214</v>
       </c>
       <c r="H14">
-        <v>9.0947033955719299</v>
+        <v>9.09470339557193</v>
       </c>
       <c r="I14">
-        <v>0.26735866069793701</v>
+        <v>0.267358660697937</v>
       </c>
       <c r="J14">
         <v>123.224116745985</v>
       </c>
       <c r="K14">
-        <v>38.299999999999997</v>
+        <v>38.3</v>
       </c>
       <c r="L14">
         <v>-5.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
-        <v>-0.48291879892349199</v>
+        <v>-0.482918798923492</v>
       </c>
       <c r="C15">
-        <v>3.6240901531605401</v>
+        <v>3.62409015316054</v>
       </c>
       <c r="D15">
-        <v>66.800445991910905</v>
+        <v>66.80044599191091</v>
       </c>
       <c r="E15">
         <v>5.55351081026072</v>
@@ -987,16 +962,16 @@
         <v>2359.51736472828</v>
       </c>
       <c r="G15">
-        <v>64.045908874831596</v>
+        <v>64.0459088748316</v>
       </c>
       <c r="H15">
-        <v>6.5926747589918904</v>
+        <v>6.59267475899189</v>
       </c>
       <c r="I15">
-        <v>0.25057727098464999</v>
+        <v>0.25057727098465</v>
       </c>
       <c r="J15">
-        <v>130.84635486674301</v>
+        <v>130.846354866743</v>
       </c>
       <c r="K15">
         <v>41.4</v>
@@ -1005,7 +980,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -1013,25 +988,25 @@
         <v>-0.438487648963928</v>
       </c>
       <c r="C16">
-        <v>4.0089702644970702</v>
+        <v>4.00897026449707</v>
       </c>
       <c r="D16">
-        <v>69.598575950205401</v>
+        <v>69.5985759502054</v>
       </c>
       <c r="E16">
-        <v>6.4222431211856703</v>
+        <v>6.42224312118567</v>
       </c>
       <c r="F16">
-        <v>2546.3846445990298</v>
+        <v>2546.38464459903</v>
       </c>
       <c r="G16">
-        <v>65.811945504155602</v>
+        <v>65.8119455041556</v>
       </c>
       <c r="H16">
-        <v>4.0845544663762299</v>
+        <v>4.08455446637623</v>
       </c>
       <c r="I16">
-        <v>-2.2347357124090202E-2</v>
+        <v>-0.0223473571240902</v>
       </c>
       <c r="J16">
         <v>135.410521454361</v>
@@ -1043,33 +1018,33 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>-0.45795029401779203</v>
+        <v>-0.457950294017792</v>
       </c>
       <c r="C17">
-        <v>-0.85305285454621405</v>
+        <v>-0.853052854546214</v>
       </c>
       <c r="D17">
-        <v>72.922851836949505</v>
+        <v>72.9228518369495</v>
       </c>
       <c r="E17">
-        <v>6.9871543059861096</v>
+        <v>6.98715430598611</v>
       </c>
       <c r="F17">
-        <v>2577.5688534011301</v>
+        <v>2577.56885340113</v>
       </c>
       <c r="G17">
-        <v>71.991376358287695</v>
+        <v>71.9913763582877</v>
       </c>
       <c r="H17">
-        <v>0.63120090517572003</v>
+        <v>0.63120090517572</v>
       </c>
       <c r="I17">
-        <v>6.3808225095272106E-2</v>
+        <v>0.06380822509527211</v>
       </c>
       <c r="J17">
         <v>144.914228195237</v>
@@ -1081,33 +1056,33 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>-0.49010601639747597</v>
+        <v>-0.490106016397476</v>
       </c>
       <c r="C18">
-        <v>0.24309985263727499</v>
+        <v>0.243099852637275</v>
       </c>
       <c r="D18">
-        <v>74.107286255618305</v>
+        <v>74.10728625561831</v>
       </c>
       <c r="E18">
-        <v>6.6900089266042402</v>
+        <v>6.69000892660424</v>
       </c>
       <c r="F18">
-        <v>2735.0604380415998</v>
+        <v>2735.0604380416</v>
       </c>
       <c r="G18">
-        <v>71.302221717499805</v>
+        <v>71.3022217174998</v>
       </c>
       <c r="H18">
         <v>2.66824816969081</v>
       </c>
       <c r="I18">
-        <v>0.22683252394199399</v>
+        <v>0.226832523941994</v>
       </c>
       <c r="J18">
         <v>145.409507973118</v>
@@ -1119,33 +1094,33 @@
         <v>-3.2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>-0.62858814001083396</v>
+        <v>-0.628588140010834</v>
       </c>
       <c r="C19">
-        <v>-0.58609520720937802</v>
+        <v>-0.586095207209378</v>
       </c>
       <c r="D19">
-        <v>81.762521835565494</v>
+        <v>81.76252183556549</v>
       </c>
       <c r="E19">
-        <v>6.9401903735920598</v>
+        <v>6.94019037359206</v>
       </c>
       <c r="F19">
-        <v>2956.1099212775298</v>
+        <v>2956.10992127753</v>
       </c>
       <c r="G19">
-        <v>79.217561823304095</v>
+        <v>79.2175618233041</v>
       </c>
       <c r="H19">
-        <v>3.5202568881162102</v>
+        <v>3.52025688811621</v>
       </c>
       <c r="I19">
-        <v>0.21110217273235299</v>
+        <v>0.211102172732353</v>
       </c>
       <c r="J19">
         <v>160.98008365887</v>
@@ -1157,36 +1132,36 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>-0.51184302568435702</v>
+        <v>-0.511843025684357</v>
       </c>
       <c r="C20">
-        <v>1.9023636753864199</v>
+        <v>1.90236367538642</v>
       </c>
       <c r="D20">
-        <v>84.423456083336504</v>
+        <v>84.4234560833365</v>
       </c>
       <c r="E20">
         <v>7.46500685572751</v>
       </c>
       <c r="F20">
-        <v>3222.3100312536599</v>
+        <v>3222.31003125366</v>
       </c>
       <c r="G20">
-        <v>80.240480692556503</v>
+        <v>80.2404806925565</v>
       </c>
       <c r="H20">
-        <v>3.5396280594263798</v>
+        <v>3.53962805942638</v>
       </c>
       <c r="I20">
-        <v>3.3082962036132799E-2</v>
+        <v>0.0330829620361328</v>
       </c>
       <c r="J20">
-        <v>164.66393677589301</v>
+        <v>164.663936775893</v>
       </c>
       <c r="K20">
         <v>43.8</v>
@@ -1195,36 +1170,36 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>-0.54622107744216897</v>
+        <v>-0.546221077442169</v>
       </c>
       <c r="C21">
         <v>3.91824395534243</v>
       </c>
       <c r="D21">
-        <v>85.157587407341097</v>
+        <v>85.1575874073411</v>
       </c>
       <c r="E21">
         <v>7.35926270105006</v>
       </c>
       <c r="F21">
-        <v>3440.9002537543402</v>
+        <v>3440.90025375434</v>
       </c>
       <c r="G21">
-        <v>79.546627624066801</v>
+        <v>79.5466276240668</v>
       </c>
       <c r="H21">
-        <v>2.7958236745224898</v>
+        <v>2.79582367452249</v>
       </c>
       <c r="I21">
-        <v>3.9987403899431201E-2</v>
+        <v>0.0399874038994312</v>
       </c>
       <c r="J21">
-        <v>164.70421503140801</v>
+        <v>164.704215031408</v>
       </c>
       <c r="K21">
         <v>41</v>
@@ -1233,7 +1208,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -1241,28 +1216,28 @@
         <v>-0.374517351388931</v>
       </c>
       <c r="C22">
-        <v>4.3448690655337296</v>
+        <v>4.34486906553373</v>
       </c>
       <c r="D22">
-        <v>84.381598008956999</v>
+        <v>84.381598008957</v>
       </c>
       <c r="E22">
-        <v>2.8654132091227198</v>
+        <v>2.86541320912272</v>
       </c>
       <c r="F22">
-        <v>3534.0395348264701</v>
+        <v>3534.03953482647</v>
       </c>
       <c r="G22">
-        <v>78.864264805977896</v>
+        <v>78.8642648059779</v>
       </c>
       <c r="H22">
-        <v>3.2209343665251602</v>
+        <v>3.22093436652516</v>
       </c>
       <c r="I22">
-        <v>-3.8989063352346399E-2</v>
+        <v>-0.0389890633523464</v>
       </c>
       <c r="J22">
-        <v>163.24586281493501</v>
+        <v>163.245862814935</v>
       </c>
       <c r="K22">
         <v>41.3</v>
@@ -1271,59 +1246,59 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>-0.30816328525543202</v>
+        <v>-0.308163285255432</v>
       </c>
       <c r="C23">
         <v>-1.26284279203588</v>
       </c>
       <c r="D23">
-        <v>93.850207127557496</v>
+        <v>93.8502071275575</v>
       </c>
       <c r="E23">
-        <v>2.5537285264813101</v>
+        <v>2.55372852648131</v>
       </c>
       <c r="F23">
-        <v>3704.1935590038001</v>
+        <v>3704.1935590038</v>
       </c>
       <c r="G23">
-        <v>92.825625709256798</v>
+        <v>92.8256257092568</v>
       </c>
       <c r="H23">
-        <v>1.8347155481044599</v>
+        <v>1.83471554810446</v>
       </c>
       <c r="I23">
-        <v>-0.11778243631124501</v>
+        <v>-0.117782436311245</v>
       </c>
       <c r="J23">
-        <v>186.67583283681401</v>
+        <v>186.675832836814</v>
       </c>
       <c r="K23">
-        <v>39.200000000000003</v>
+        <v>39.2</v>
       </c>
       <c r="L23">
         <v>-1.4</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>-0.28725433349609403</v>
+        <v>-0.287254333496094</v>
       </c>
       <c r="C24">
-        <v>0.33910174697936202</v>
+        <v>0.339101746979362</v>
       </c>
       <c r="D24">
-        <v>93.420129043510997</v>
+        <v>93.420129043511</v>
       </c>
       <c r="E24">
-        <v>8.5375004675578801</v>
+        <v>8.53750046755788</v>
       </c>
       <c r="F24">
         <v>4147.69777213621</v>
@@ -1332,10 +1307,10 @@
         <v>89.7334901043249</v>
       </c>
       <c r="H24">
-        <v>3.1565074996312701</v>
+        <v>3.15650749963127</v>
       </c>
       <c r="I24">
-        <v>-4.61320951581001E-2</v>
+        <v>-0.0461320951581001</v>
       </c>
       <c r="J24">
         <v>183.153619147836</v>
@@ -1347,65 +1322,60 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>-0.41581428050994901</v>
+        <v>-0.415814280509949</v>
       </c>
       <c r="C25">
         <v>5.94503707253957</v>
       </c>
       <c r="D25">
-        <v>86.467419237129704</v>
+        <v>86.4674192371297</v>
       </c>
       <c r="E25">
-        <v>5.0650239145507499</v>
+        <v>5.06502391455075</v>
       </c>
       <c r="F25">
-        <v>4323.3503198245098</v>
+        <v>4323.35031982451</v>
       </c>
       <c r="G25">
-        <v>78.350652032764202</v>
+        <v>78.3506520327642</v>
       </c>
       <c r="H25">
-        <v>3.2528928266766099</v>
+        <v>3.25289282667661</v>
       </c>
       <c r="I25">
-        <v>-3.6380734294652897E-2</v>
+        <v>-0.0363807342946529</v>
       </c>
       <c r="J25">
-        <v>164.81807126989401</v>
+        <v>164.818071269894</v>
       </c>
       <c r="K25">
-        <v>34.299999999999997</v>
+        <v>34.3</v>
       </c>
       <c r="L25">
         <v>-1.7</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
-        <v>5.8874250486657296</v>
-      </c>
-      <c r="D26" s="2"/>
+        <v>5.88742504866573</v>
+      </c>
       <c r="E26">
-        <v>7.0911874663397496</v>
+        <v>7.09118746633975</v>
       </c>
       <c r="F26">
-        <v>4717.2902873244902</v>
-      </c>
-      <c r="G26" s="2"/>
+        <v>4717.29028732449</v>
+      </c>
       <c r="H26">
-        <v>3.6210927388584699</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+        <v>3.62109273885847</v>
+      </c>
       <c r="K26">
         <v>31.3</v>
       </c>

--- a/VNM_WB_timeseries.xlsx
+++ b/VNM_WB_timeseries.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youne\https-github.com-Youncki25-credit-rating-app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600D310D-7A16-4275-B0FB-37404C4CF2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -58,8 +77,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,13 +141,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -166,7 +193,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -200,6 +227,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,9 +262,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,11 +438,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="13" width="39.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -454,33 +486,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>-0.584863126277924</v>
+        <v>-0.58486312627792403</v>
       </c>
       <c r="C2">
-        <v>3.54799694298148</v>
+        <v>3.5479969429814799</v>
       </c>
       <c r="D2">
-        <v>53.9214970089166</v>
+        <v>53.921497008916603</v>
       </c>
       <c r="E2">
-        <v>6.78731640463151</v>
+        <v>6.7873164046315102</v>
       </c>
       <c r="F2">
         <v>404.029784055118</v>
       </c>
       <c r="G2">
-        <v>57.4955974105958</v>
+        <v>57.495597410595799</v>
       </c>
       <c r="H2">
         <v>-1.8</v>
       </c>
       <c r="I2">
-        <v>0.408773571252823</v>
+        <v>0.40877357125282299</v>
       </c>
       <c r="J2">
         <v>111.417094419512</v>
@@ -492,7 +524,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
@@ -500,16 +532,16 @@
         <v>2.08657136826562</v>
       </c>
       <c r="D3">
-        <v>55.0619332820827</v>
+        <v>55.061933282082698</v>
       </c>
       <c r="E3">
-        <v>6.19289331233377</v>
+        <v>6.1928933123337702</v>
       </c>
       <c r="F3">
-        <v>419.205677580901</v>
+        <v>419.20567758090101</v>
       </c>
       <c r="G3">
-        <v>56.8940047164421</v>
+        <v>56.894004716442097</v>
       </c>
       <c r="H3">
         <v>-0.4</v>
@@ -521,10 +553,10 @@
         <v>25.4</v>
       </c>
       <c r="L3">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>-2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -532,28 +564,28 @@
         <v>-0.560990810394287</v>
       </c>
       <c r="C4">
-        <v>-1.72255927072095</v>
+        <v>-1.7225592707209501</v>
       </c>
       <c r="D4">
-        <v>54.7391336880928</v>
+        <v>54.739133688092799</v>
       </c>
       <c r="E4">
         <v>6.32082099160833</v>
       </c>
       <c r="F4">
-        <v>445.132861817313</v>
+        <v>445.13286181731303</v>
       </c>
       <c r="G4">
-        <v>61.9577349644058</v>
+        <v>61.957734964405802</v>
       </c>
       <c r="H4">
         <v>3.8</v>
       </c>
       <c r="I4">
-        <v>0.353681147098541</v>
+        <v>0.35368114709854098</v>
       </c>
       <c r="J4">
-        <v>116.696868652499</v>
+        <v>116.69686865249901</v>
       </c>
       <c r="K4">
         <v>27.7</v>
@@ -562,7 +594,7 @@
         <v>-1.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
@@ -570,28 +602,28 @@
         <v>-0.49087256193161</v>
       </c>
       <c r="C5">
-        <v>-4.88211706972335</v>
+        <v>-4.8821170697233498</v>
       </c>
       <c r="D5">
         <v>56.6732579147533</v>
       </c>
       <c r="E5">
-        <v>6.89906349055258</v>
+        <v>6.8990634905525798</v>
       </c>
       <c r="F5">
-        <v>497.117089249256</v>
+        <v>497.11708924925603</v>
       </c>
       <c r="G5">
-        <v>67.6546965243715</v>
+        <v>67.654696524371502</v>
       </c>
       <c r="H5">
-        <v>3.23464817293926</v>
+        <v>3.2346481729392602</v>
       </c>
       <c r="I5">
-        <v>0.126424372196198</v>
+        <v>0.12642437219619801</v>
       </c>
       <c r="J5">
-        <v>124.327954439125</v>
+        <v>124.32795443912499</v>
       </c>
       <c r="K5">
         <v>29.8</v>
@@ -600,12 +632,12 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>-0.756660282611847</v>
+        <v>-0.75666028261184703</v>
       </c>
       <c r="C6">
         <v>-2.10663701040253</v>
@@ -614,16 +646,16 @@
         <v>59.7310414143857</v>
       </c>
       <c r="E6">
-        <v>7.53641060890386</v>
+        <v>7.5364106089038598</v>
       </c>
       <c r="F6">
-        <v>565.452284586212</v>
+        <v>565.45228458621204</v>
       </c>
       <c r="G6">
-        <v>73.28545645436159</v>
+        <v>73.285456454361594</v>
       </c>
       <c r="H6">
-        <v>7.75494748709601</v>
+        <v>7.7549474870960102</v>
       </c>
       <c r="I6">
         <v>0.150153517723083</v>
@@ -638,36 +670,36 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>-0.7295823097228999</v>
+        <v>-0.72958230972289995</v>
       </c>
       <c r="C7">
-        <v>-0.971989162897001</v>
+        <v>-0.97198916289700099</v>
       </c>
       <c r="D7">
         <v>63.6994926701393</v>
       </c>
       <c r="E7">
-        <v>7.54724772895918</v>
+        <v>7.5472477289591797</v>
       </c>
       <c r="F7">
-        <v>710.746759994861</v>
+        <v>710.74675999486101</v>
       </c>
       <c r="G7">
-        <v>67.0153533748869</v>
+        <v>67.015353374886899</v>
       </c>
       <c r="H7">
-        <v>8.284572431286771</v>
+        <v>8.2845724312867706</v>
       </c>
       <c r="I7">
-        <v>0.484037667512894</v>
+        <v>0.48403766751289401</v>
       </c>
       <c r="J7">
-        <v>130.714846045026</v>
+        <v>130.71484604502601</v>
       </c>
       <c r="K7">
         <v>28.7</v>
@@ -676,36 +708,36 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>-0.747617363929749</v>
+        <v>-0.74761736392974898</v>
       </c>
       <c r="C8">
-        <v>-0.246704373698266</v>
+        <v>-0.24670437369826601</v>
       </c>
       <c r="D8">
-        <v>67.71681432601871</v>
+        <v>67.716814326018707</v>
       </c>
       <c r="E8">
-        <v>6.97795481056711</v>
+        <v>6.9779548105671099</v>
       </c>
       <c r="F8">
-        <v>807.7566451170539</v>
+        <v>807.75664511705395</v>
       </c>
       <c r="G8">
-        <v>70.5968075435795</v>
+        <v>70.596807543579501</v>
       </c>
       <c r="H8">
         <v>7.41801715108463</v>
       </c>
       <c r="I8">
-        <v>0.405120253562927</v>
+        <v>0.40512025356292702</v>
       </c>
       <c r="J8">
-        <v>138.313621869598</v>
+        <v>138.31362186959799</v>
       </c>
       <c r="K8">
         <v>30.2</v>
@@ -714,74 +746,74 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>-0.630165636539459</v>
+        <v>-0.63016563653945901</v>
       </c>
       <c r="C9">
-        <v>-8.98165936412439</v>
+        <v>-8.9816593641243898</v>
       </c>
       <c r="D9">
-        <v>70.517874602272</v>
+        <v>70.517874602272002</v>
       </c>
       <c r="E9">
-        <v>7.12950448605439</v>
+        <v>7.1295044860543904</v>
       </c>
       <c r="F9">
-        <v>925.640338348717</v>
+        <v>925.64033834871702</v>
       </c>
       <c r="G9">
-        <v>84.08750939428231</v>
+        <v>84.087509394282307</v>
       </c>
       <c r="H9">
-        <v>8.344448897738371</v>
+        <v>8.3444488977383706</v>
       </c>
       <c r="I9">
-        <v>0.251871973276138</v>
+        <v>0.25187197327613797</v>
       </c>
       <c r="J9">
         <v>154.605383996554</v>
       </c>
       <c r="K9">
-        <v>32.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="L9">
         <v>-1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>-0.711532890796661</v>
+        <v>-0.71153289079666104</v>
       </c>
       <c r="C10">
         <v>-10.9179529896098</v>
       </c>
       <c r="D10">
-        <v>70.33669194027151</v>
+        <v>70.336691940271507</v>
       </c>
       <c r="E10">
-        <v>5.66177120891362</v>
+        <v>5.6617712089136196</v>
       </c>
       <c r="F10">
         <v>1163.83195772873</v>
       </c>
       <c r="G10">
-        <v>83.9807876874868</v>
+        <v>83.980787687486796</v>
       </c>
       <c r="H10">
         <v>23.1154483474477</v>
       </c>
       <c r="I10">
-        <v>0.165260821580887</v>
+        <v>0.16526082158088701</v>
       </c>
       <c r="J10">
-        <v>154.317479627758</v>
+        <v>154.31747962775799</v>
       </c>
       <c r="K10">
         <v>31</v>
@@ -790,170 +822,170 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>-0.545064032077789</v>
+        <v>-0.54506403207778897</v>
       </c>
       <c r="C11">
         <v>-6.23310024019381</v>
       </c>
       <c r="D11">
-        <v>62.6088840664865</v>
+        <v>62.608884066486503</v>
       </c>
       <c r="E11">
-        <v>5.39789754014181</v>
+        <v>5.3978975401418099</v>
       </c>
       <c r="F11">
-        <v>1226.16976051536</v>
+        <v>1226.1697605153599</v>
       </c>
       <c r="G11">
-        <v>72.0974336552711</v>
+        <v>72.097433655271104</v>
       </c>
       <c r="H11">
         <v>6.71698269988629</v>
       </c>
       <c r="I11">
-        <v>0.271775960922241</v>
+        <v>0.27177596092224099</v>
       </c>
       <c r="J11">
-        <v>134.706317721758</v>
+        <v>134.70631772175801</v>
       </c>
       <c r="K11">
-        <v>36.2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="L11">
         <v>-4.8</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
-        <v>-0.6225432753562929</v>
+        <v>-0.62254327535629295</v>
       </c>
       <c r="C12">
-        <v>-2.90486815229253</v>
+        <v>-2.9048681522925301</v>
       </c>
       <c r="D12">
-        <v>54.1758459668515</v>
+        <v>54.175845966851497</v>
       </c>
       <c r="E12">
-        <v>6.42324482239482</v>
+        <v>6.4232448223948202</v>
       </c>
       <c r="F12">
-        <v>1683.16182443979</v>
+        <v>1683.1618244397901</v>
       </c>
       <c r="G12">
-        <v>59.8018415728627</v>
+        <v>59.801841572862699</v>
       </c>
       <c r="H12">
-        <v>9.207466487784149</v>
+        <v>9.2074664877841492</v>
       </c>
       <c r="I12">
-        <v>0.148407876491547</v>
+        <v>0.14840787649154699</v>
       </c>
       <c r="J12">
         <v>113.977687539714</v>
       </c>
       <c r="K12">
-        <v>37.3</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="L12">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>-2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>-0.614729940891266</v>
+        <v>-0.61472994089126598</v>
       </c>
       <c r="C13">
-        <v>0.136736251193688</v>
+        <v>0.13673625119368801</v>
       </c>
       <c r="D13">
-        <v>61.1801557211956</v>
+        <v>61.180155721195597</v>
       </c>
       <c r="E13">
-        <v>6.41316889681683</v>
+        <v>6.4131688968168303</v>
       </c>
       <c r="F13">
-        <v>1950.92504174913</v>
+        <v>1950.9250417491301</v>
       </c>
       <c r="G13">
-        <v>64.0804222196337</v>
+        <v>64.080422219633704</v>
       </c>
       <c r="H13">
-        <v>18.6777322770707</v>
+        <v>18.677732277070699</v>
       </c>
       <c r="I13">
-        <v>0.189088448882103</v>
+        <v>0.18908844888210299</v>
       </c>
       <c r="J13">
-        <v>125.260577940829</v>
+        <v>125.26057794082899</v>
       </c>
       <c r="K13">
-        <v>36.2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="L13">
         <v>-0.9</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>-0.5321059823036191</v>
+        <v>-0.53210598230361905</v>
       </c>
       <c r="C14">
-        <v>4.82078231422777</v>
+        <v>4.8207823142277704</v>
       </c>
       <c r="D14">
-        <v>63.4739249038633</v>
+        <v>63.473924903863299</v>
       </c>
       <c r="E14">
-        <v>5.5045447041189</v>
+        <v>5.5045447041189002</v>
       </c>
       <c r="F14">
         <v>2185.11767654291</v>
       </c>
       <c r="G14">
-        <v>59.7501918421214</v>
+        <v>59.750191842121403</v>
       </c>
       <c r="H14">
-        <v>9.09470339557193</v>
+        <v>9.0947033955719299</v>
       </c>
       <c r="I14">
-        <v>0.267358660697937</v>
+        <v>0.26735866069793701</v>
       </c>
       <c r="J14">
         <v>123.224116745985</v>
       </c>
       <c r="K14">
-        <v>38.3</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="L14">
         <v>-5.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
-        <v>-0.482918798923492</v>
+        <v>-0.48291879892349199</v>
       </c>
       <c r="C15">
-        <v>3.62409015316054</v>
+        <v>3.6240901531605401</v>
       </c>
       <c r="D15">
-        <v>66.80044599191091</v>
+        <v>66.800445991910905</v>
       </c>
       <c r="E15">
         <v>5.55351081026072</v>
@@ -962,16 +994,16 @@
         <v>2359.51736472828</v>
       </c>
       <c r="G15">
-        <v>64.0459088748316</v>
+        <v>64.045908874831596</v>
       </c>
       <c r="H15">
-        <v>6.59267475899189</v>
+        <v>6.5926747589918904</v>
       </c>
       <c r="I15">
-        <v>0.25057727098465</v>
+        <v>0.25057727098464999</v>
       </c>
       <c r="J15">
-        <v>130.846354866743</v>
+        <v>130.84635486674301</v>
       </c>
       <c r="K15">
         <v>41.4</v>
@@ -980,7 +1012,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -988,25 +1020,25 @@
         <v>-0.438487648963928</v>
       </c>
       <c r="C16">
-        <v>4.00897026449707</v>
+        <v>4.0089702644970702</v>
       </c>
       <c r="D16">
-        <v>69.5985759502054</v>
+        <v>69.598575950205401</v>
       </c>
       <c r="E16">
-        <v>6.42224312118567</v>
+        <v>6.4222431211856703</v>
       </c>
       <c r="F16">
-        <v>2546.38464459903</v>
+        <v>2546.3846445990298</v>
       </c>
       <c r="G16">
-        <v>65.8119455041556</v>
+        <v>65.811945504155602</v>
       </c>
       <c r="H16">
-        <v>4.08455446637623</v>
+        <v>4.0845544663762299</v>
       </c>
       <c r="I16">
-        <v>-0.0223473571240902</v>
+        <v>-2.2347357124090202E-2</v>
       </c>
       <c r="J16">
         <v>135.410521454361</v>
@@ -1018,33 +1050,33 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>-0.457950294017792</v>
+        <v>-0.45795029401779203</v>
       </c>
       <c r="C17">
-        <v>-0.853052854546214</v>
+        <v>-0.85305285454621405</v>
       </c>
       <c r="D17">
-        <v>72.9228518369495</v>
+        <v>72.922851836949505</v>
       </c>
       <c r="E17">
-        <v>6.98715430598611</v>
+        <v>6.9871543059861096</v>
       </c>
       <c r="F17">
-        <v>2577.56885340113</v>
+        <v>2577.5688534011301</v>
       </c>
       <c r="G17">
-        <v>71.9913763582877</v>
+        <v>71.991376358287695</v>
       </c>
       <c r="H17">
-        <v>0.63120090517572</v>
+        <v>0.63120090517572003</v>
       </c>
       <c r="I17">
-        <v>0.06380822509527211</v>
+        <v>6.3808225095272106E-2</v>
       </c>
       <c r="J17">
         <v>144.914228195237</v>
@@ -1056,33 +1088,33 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>-0.490106016397476</v>
+        <v>-0.49010601639747597</v>
       </c>
       <c r="C18">
-        <v>0.243099852637275</v>
+        <v>0.24309985263727499</v>
       </c>
       <c r="D18">
-        <v>74.10728625561831</v>
+        <v>74.107286255618305</v>
       </c>
       <c r="E18">
-        <v>6.69000892660424</v>
+        <v>6.6900089266042402</v>
       </c>
       <c r="F18">
-        <v>2735.0604380416</v>
+        <v>2735.0604380415998</v>
       </c>
       <c r="G18">
-        <v>71.3022217174998</v>
+        <v>71.302221717499805</v>
       </c>
       <c r="H18">
         <v>2.66824816969081</v>
       </c>
       <c r="I18">
-        <v>0.226832523941994</v>
+        <v>0.22683252394199399</v>
       </c>
       <c r="J18">
         <v>145.409507973118</v>
@@ -1094,33 +1126,33 @@
         <v>-3.2</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>-0.628588140010834</v>
+        <v>-0.62858814001083396</v>
       </c>
       <c r="C19">
-        <v>-0.586095207209378</v>
+        <v>-0.58609520720937802</v>
       </c>
       <c r="D19">
-        <v>81.76252183556549</v>
+        <v>81.762521835565494</v>
       </c>
       <c r="E19">
-        <v>6.94019037359206</v>
+        <v>6.9401903735920598</v>
       </c>
       <c r="F19">
-        <v>2956.10992127753</v>
+        <v>2956.1099212775298</v>
       </c>
       <c r="G19">
-        <v>79.2175618233041</v>
+        <v>79.217561823304095</v>
       </c>
       <c r="H19">
-        <v>3.52025688811621</v>
+        <v>3.5202568881162102</v>
       </c>
       <c r="I19">
-        <v>0.211102172732353</v>
+        <v>0.21110217273235299</v>
       </c>
       <c r="J19">
         <v>160.98008365887</v>
@@ -1132,36 +1164,36 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>-0.511843025684357</v>
+        <v>-0.51184302568435702</v>
       </c>
       <c r="C20">
-        <v>1.90236367538642</v>
+        <v>1.9023636753864199</v>
       </c>
       <c r="D20">
-        <v>84.4234560833365</v>
+        <v>84.423456083336504</v>
       </c>
       <c r="E20">
         <v>7.46500685572751</v>
       </c>
       <c r="F20">
-        <v>3222.31003125366</v>
+        <v>3222.3100312536599</v>
       </c>
       <c r="G20">
-        <v>80.2404806925565</v>
+        <v>80.240480692556503</v>
       </c>
       <c r="H20">
-        <v>3.53962805942638</v>
+        <v>3.5396280594263798</v>
       </c>
       <c r="I20">
-        <v>0.0330829620361328</v>
+        <v>3.3082962036132799E-2</v>
       </c>
       <c r="J20">
-        <v>164.663936775893</v>
+        <v>164.66393677589301</v>
       </c>
       <c r="K20">
         <v>43.8</v>
@@ -1170,36 +1202,36 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>-0.546221077442169</v>
+        <v>-0.54622107744216897</v>
       </c>
       <c r="C21">
         <v>3.91824395534243</v>
       </c>
       <c r="D21">
-        <v>85.1575874073411</v>
+        <v>85.157587407341097</v>
       </c>
       <c r="E21">
         <v>7.35926270105006</v>
       </c>
       <c r="F21">
-        <v>3440.90025375434</v>
+        <v>3440.9002537543402</v>
       </c>
       <c r="G21">
-        <v>79.5466276240668</v>
+        <v>79.546627624066801</v>
       </c>
       <c r="H21">
-        <v>2.79582367452249</v>
+        <v>2.7958236745224898</v>
       </c>
       <c r="I21">
-        <v>0.0399874038994312</v>
+        <v>3.9987403899431201E-2</v>
       </c>
       <c r="J21">
-        <v>164.704215031408</v>
+        <v>164.70421503140801</v>
       </c>
       <c r="K21">
         <v>41</v>
@@ -1208,7 +1240,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -1216,28 +1248,28 @@
         <v>-0.374517351388931</v>
       </c>
       <c r="C22">
-        <v>4.34486906553373</v>
+        <v>4.3448690655337296</v>
       </c>
       <c r="D22">
-        <v>84.381598008957</v>
+        <v>84.381598008956999</v>
       </c>
       <c r="E22">
-        <v>2.86541320912272</v>
+        <v>2.8654132091227198</v>
       </c>
       <c r="F22">
-        <v>3534.03953482647</v>
+        <v>3534.0395348264701</v>
       </c>
       <c r="G22">
-        <v>78.8642648059779</v>
+        <v>78.864264805977896</v>
       </c>
       <c r="H22">
-        <v>3.22093436652516</v>
+        <v>3.2209343665251602</v>
       </c>
       <c r="I22">
-        <v>-0.0389890633523464</v>
+        <v>-3.8989063352346399E-2</v>
       </c>
       <c r="J22">
-        <v>163.245862814935</v>
+        <v>163.24586281493501</v>
       </c>
       <c r="K22">
         <v>41.3</v>
@@ -1246,59 +1278,59 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>-0.308163285255432</v>
+        <v>-0.30816328525543202</v>
       </c>
       <c r="C23">
         <v>-1.26284279203588</v>
       </c>
       <c r="D23">
-        <v>93.8502071275575</v>
+        <v>93.850207127557496</v>
       </c>
       <c r="E23">
-        <v>2.55372852648131</v>
+        <v>2.5537285264813101</v>
       </c>
       <c r="F23">
-        <v>3704.1935590038</v>
+        <v>3704.1935590038001</v>
       </c>
       <c r="G23">
-        <v>92.8256257092568</v>
+        <v>92.825625709256798</v>
       </c>
       <c r="H23">
-        <v>1.83471554810446</v>
+        <v>1.8347155481044599</v>
       </c>
       <c r="I23">
-        <v>-0.117782436311245</v>
+        <v>-0.11778243631124501</v>
       </c>
       <c r="J23">
-        <v>186.675832836814</v>
+        <v>186.67583283681401</v>
       </c>
       <c r="K23">
-        <v>39.2</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="L23">
         <v>-1.4</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>-0.287254333496094</v>
+        <v>-0.28725433349609403</v>
       </c>
       <c r="C24">
-        <v>0.339101746979362</v>
+        <v>0.33910174697936202</v>
       </c>
       <c r="D24">
-        <v>93.420129043511</v>
+        <v>93.420129043510997</v>
       </c>
       <c r="E24">
-        <v>8.53750046755788</v>
+        <v>8.5375004675578801</v>
       </c>
       <c r="F24">
         <v>4147.69777213621</v>
@@ -1307,10 +1339,10 @@
         <v>89.7334901043249</v>
       </c>
       <c r="H24">
-        <v>3.15650749963127</v>
+        <v>3.1565074996312701</v>
       </c>
       <c r="I24">
-        <v>-0.0461320951581001</v>
+        <v>-4.61320951581001E-2</v>
       </c>
       <c r="J24">
         <v>183.153619147836</v>
@@ -1322,59 +1354,71 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>-0.415814280509949</v>
+        <v>-0.41581428050994901</v>
       </c>
       <c r="C25">
         <v>5.94503707253957</v>
       </c>
       <c r="D25">
-        <v>86.4674192371297</v>
+        <v>86.467419237129704</v>
       </c>
       <c r="E25">
-        <v>5.06502391455075</v>
+        <v>5.0650239145507499</v>
       </c>
       <c r="F25">
-        <v>4323.35031982451</v>
+        <v>4323.3503198245098</v>
       </c>
       <c r="G25">
-        <v>78.3506520327642</v>
+        <v>78.350652032764202</v>
       </c>
       <c r="H25">
-        <v>3.25289282667661</v>
+        <v>3.2528928266766099</v>
       </c>
       <c r="I25">
-        <v>-0.0363807342946529</v>
+        <v>-3.6380734294652897E-2</v>
       </c>
       <c r="J25">
-        <v>164.818071269894</v>
+        <v>164.81807126989401</v>
       </c>
       <c r="K25">
-        <v>34.3</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="L25">
         <v>-1.7</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
+      <c r="B26">
+        <f>AVERAGEA(B2:B25)</f>
+        <v>-0.54211271586625476</v>
+      </c>
       <c r="C26">
-        <v>5.88742504866573</v>
+        <v>5.8874250486657296</v>
+      </c>
+      <c r="D26">
+        <f>D25</f>
+        <v>86.467419237129704</v>
       </c>
       <c r="E26">
-        <v>7.09118746633975</v>
+        <v>7.0911874663397496</v>
       </c>
       <c r="F26">
-        <v>4717.29028732449</v>
+        <v>4717.2902873244902</v>
+      </c>
+      <c r="G26">
+        <f>AVERAGEA(G2:G25)</f>
+        <v>72.109499691971962</v>
       </c>
       <c r="H26">
-        <v>3.62109273885847</v>
+        <v>3.6210927388584699</v>
       </c>
       <c r="K26">
         <v>31.3</v>
